--- a/AAII_Financials/Yearly/IRS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IRS_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>252700</v>
+        <v>105400</v>
       </c>
       <c r="E8" s="3">
-        <v>195700</v>
+        <v>81600</v>
       </c>
       <c r="F8" s="3">
-        <v>129800</v>
+        <v>54100</v>
       </c>
       <c r="G8" s="3">
-        <v>98700</v>
+        <v>41100</v>
       </c>
       <c r="H8" s="3">
-        <v>79300</v>
+        <v>33000</v>
       </c>
       <c r="I8" s="3">
-        <v>166500</v>
+        <v>69400</v>
       </c>
       <c r="J8" s="3">
-        <v>168900</v>
+        <v>70400</v>
       </c>
       <c r="K8" s="3">
         <v>36900</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>87200</v>
+        <v>36300</v>
       </c>
       <c r="E9" s="3">
-        <v>74100</v>
+        <v>30900</v>
       </c>
       <c r="F9" s="3">
-        <v>67600</v>
+        <v>28200</v>
       </c>
       <c r="G9" s="3">
-        <v>42600</v>
+        <v>17700</v>
       </c>
       <c r="H9" s="3">
-        <v>29600</v>
+        <v>12300</v>
       </c>
       <c r="I9" s="3">
-        <v>98000</v>
+        <v>40900</v>
       </c>
       <c r="J9" s="3">
-        <v>235200</v>
+        <v>98100</v>
       </c>
       <c r="K9" s="3">
         <v>127200</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>165500</v>
+        <v>69000</v>
       </c>
       <c r="E10" s="3">
-        <v>121600</v>
+        <v>50700</v>
       </c>
       <c r="F10" s="3">
-        <v>62300</v>
+        <v>26000</v>
       </c>
       <c r="G10" s="3">
-        <v>56100</v>
+        <v>23400</v>
       </c>
       <c r="H10" s="3">
-        <v>49600</v>
+        <v>20700</v>
       </c>
       <c r="I10" s="3">
-        <v>68400</v>
+        <v>28500</v>
       </c>
       <c r="J10" s="3">
-        <v>-66300</v>
+        <v>-27600</v>
       </c>
       <c r="K10" s="3">
         <v>-90300</v>
@@ -951,25 +951,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>21100</v>
+        <v>8800</v>
       </c>
       <c r="E14" s="3">
-        <v>1700</v>
+        <v>700</v>
       </c>
       <c r="F14" s="3">
+        <v>200</v>
+      </c>
+      <c r="G14" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H14" s="3">
+        <v>400</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J14" s="3">
         <v>500</v>
-      </c>
-      <c r="G14" s="3">
-        <v>7500</v>
-      </c>
-      <c r="H14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="J14" s="3">
-        <v>1200</v>
       </c>
       <c r="K14" s="3">
         <v>-100</v>
@@ -993,25 +993,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="E15" s="3">
-        <v>1900</v>
+        <v>800</v>
       </c>
       <c r="F15" s="3">
-        <v>3400</v>
+        <v>1400</v>
       </c>
       <c r="G15" s="3">
-        <v>1700</v>
+        <v>700</v>
       </c>
       <c r="H15" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>7600</v>
+        <v>3200</v>
       </c>
       <c r="J15" s="3">
-        <v>9900</v>
+        <v>4100</v>
       </c>
       <c r="K15" s="3">
         <v>2300</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>326600</v>
+        <v>136200</v>
       </c>
       <c r="E17" s="3">
-        <v>36100</v>
+        <v>15100</v>
       </c>
       <c r="F17" s="3">
-        <v>189400</v>
+        <v>79000</v>
       </c>
       <c r="G17" s="3">
-        <v>-170700</v>
+        <v>-71200</v>
       </c>
       <c r="H17" s="3">
-        <v>211900</v>
+        <v>88300</v>
       </c>
       <c r="I17" s="3">
-        <v>88600</v>
+        <v>36900</v>
       </c>
       <c r="J17" s="3">
-        <v>160400</v>
+        <v>66900</v>
       </c>
       <c r="K17" s="3">
         <v>-20100</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-74000</v>
+        <v>-30800</v>
       </c>
       <c r="E18" s="3">
-        <v>159600</v>
+        <v>66600</v>
       </c>
       <c r="F18" s="3">
-        <v>-59500</v>
+        <v>-24800</v>
       </c>
       <c r="G18" s="3">
-        <v>269400</v>
+        <v>112300</v>
       </c>
       <c r="H18" s="3">
-        <v>-132600</v>
+        <v>-55300</v>
       </c>
       <c r="I18" s="3">
-        <v>77900</v>
+        <v>32500</v>
       </c>
       <c r="J18" s="3">
-        <v>8500</v>
+        <v>3500</v>
       </c>
       <c r="K18" s="3">
         <v>57100</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>85700</v>
+        <v>35700</v>
       </c>
       <c r="E20" s="3">
-        <v>120700</v>
+        <v>50300</v>
       </c>
       <c r="F20" s="3">
-        <v>87000</v>
+        <v>36300</v>
       </c>
       <c r="G20" s="3">
-        <v>31100</v>
+        <v>13000</v>
       </c>
       <c r="H20" s="3">
-        <v>-24000</v>
+        <v>-10000</v>
       </c>
       <c r="I20" s="3">
-        <v>-49300</v>
+        <v>-20600</v>
       </c>
       <c r="J20" s="3">
-        <v>16700</v>
+        <v>6900</v>
       </c>
       <c r="K20" s="3">
         <v>-7500</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>17100</v>
+        <v>7100</v>
       </c>
       <c r="E21" s="3">
-        <v>286100</v>
+        <v>119300</v>
       </c>
       <c r="F21" s="3">
-        <v>33900</v>
+        <v>14100</v>
       </c>
       <c r="G21" s="3">
-        <v>303800</v>
+        <v>126700</v>
       </c>
       <c r="H21" s="3">
-        <v>-155000</v>
+        <v>-64600</v>
       </c>
       <c r="I21" s="3">
-        <v>47800</v>
+        <v>19900</v>
       </c>
       <c r="J21" s="3">
-        <v>34700</v>
+        <v>14500</v>
       </c>
       <c r="K21" s="3">
         <v>54000</v>
@@ -1236,25 +1236,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>34300</v>
+        <v>14300</v>
       </c>
       <c r="E22" s="3">
-        <v>50600</v>
+        <v>21100</v>
       </c>
       <c r="F22" s="3">
-        <v>97500</v>
+        <v>40600</v>
       </c>
       <c r="G22" s="3">
-        <v>65400</v>
+        <v>27300</v>
       </c>
       <c r="H22" s="3">
-        <v>18900</v>
+        <v>7900</v>
       </c>
       <c r="I22" s="3">
-        <v>38300</v>
+        <v>16000</v>
       </c>
       <c r="J22" s="3">
-        <v>37300</v>
+        <v>15600</v>
       </c>
       <c r="K22" s="3">
         <v>6700</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-22600</v>
+        <v>-9400</v>
       </c>
       <c r="E23" s="3">
-        <v>229800</v>
+        <v>95800</v>
       </c>
       <c r="F23" s="3">
-        <v>-70000</v>
+        <v>-29200</v>
       </c>
       <c r="G23" s="3">
-        <v>235100</v>
+        <v>98000</v>
       </c>
       <c r="H23" s="3">
-        <v>-175500</v>
+        <v>-73200</v>
       </c>
       <c r="I23" s="3">
-        <v>-9700</v>
+        <v>-4000</v>
       </c>
       <c r="J23" s="3">
-        <v>-12200</v>
+        <v>-5100</v>
       </c>
       <c r="K23" s="3">
         <v>42900</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-187000</v>
+        <v>-78000</v>
       </c>
       <c r="E24" s="3">
-        <v>16900</v>
+        <v>7000</v>
       </c>
       <c r="F24" s="3">
-        <v>216800</v>
+        <v>90400</v>
       </c>
       <c r="G24" s="3">
-        <v>46700</v>
+        <v>19500</v>
       </c>
       <c r="H24" s="3">
-        <v>-19100</v>
+        <v>-8000</v>
       </c>
       <c r="I24" s="3">
-        <v>-17800</v>
+        <v>-7400</v>
       </c>
       <c r="J24" s="3">
-        <v>4200</v>
+        <v>1800</v>
       </c>
       <c r="K24" s="3">
         <v>18100</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>164400</v>
+        <v>68600</v>
       </c>
       <c r="E26" s="3">
-        <v>212900</v>
+        <v>88800</v>
       </c>
       <c r="F26" s="3">
-        <v>-286800</v>
+        <v>-119600</v>
       </c>
       <c r="G26" s="3">
-        <v>188400</v>
+        <v>78600</v>
       </c>
       <c r="H26" s="3">
-        <v>-156400</v>
+        <v>-65200</v>
       </c>
       <c r="I26" s="3">
-        <v>8100</v>
+        <v>3400</v>
       </c>
       <c r="J26" s="3">
-        <v>-16400</v>
+        <v>-6800</v>
       </c>
       <c r="K26" s="3">
         <v>24800</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>162300</v>
+        <v>67700</v>
       </c>
       <c r="E27" s="3">
-        <v>210800</v>
+        <v>87900</v>
       </c>
       <c r="F27" s="3">
-        <v>-210100</v>
+        <v>-87600</v>
       </c>
       <c r="G27" s="3">
-        <v>122300</v>
+        <v>51000</v>
       </c>
       <c r="H27" s="3">
-        <v>-148900</v>
+        <v>-62100</v>
       </c>
       <c r="I27" s="3">
-        <v>-16000</v>
+        <v>-6700</v>
       </c>
       <c r="J27" s="3">
-        <v>-28200</v>
+        <v>-11700</v>
       </c>
       <c r="K27" s="3">
         <v>23300</v>
@@ -1536,19 +1536,19 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-89300</v>
+        <v>-37200</v>
       </c>
       <c r="G29" s="3">
-        <v>-23000</v>
+        <v>-9600</v>
       </c>
       <c r="H29" s="3">
-        <v>-6700</v>
+        <v>-2800</v>
       </c>
       <c r="I29" s="3">
-        <v>57700</v>
+        <v>24000</v>
       </c>
       <c r="J29" s="3">
-        <v>25000</v>
+        <v>10400</v>
       </c>
       <c r="K29" s="3">
         <v>2300</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-85700</v>
+        <v>-35700</v>
       </c>
       <c r="E32" s="3">
-        <v>-120700</v>
+        <v>-50300</v>
       </c>
       <c r="F32" s="3">
-        <v>-87000</v>
+        <v>-36300</v>
       </c>
       <c r="G32" s="3">
-        <v>-31100</v>
+        <v>-13000</v>
       </c>
       <c r="H32" s="3">
-        <v>24000</v>
+        <v>10000</v>
       </c>
       <c r="I32" s="3">
-        <v>49300</v>
+        <v>20600</v>
       </c>
       <c r="J32" s="3">
-        <v>-16700</v>
+        <v>-6900</v>
       </c>
       <c r="K32" s="3">
         <v>7500</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>162300</v>
+        <v>67700</v>
       </c>
       <c r="E33" s="3">
-        <v>210800</v>
+        <v>87900</v>
       </c>
       <c r="F33" s="3">
-        <v>-299400</v>
+        <v>-124800</v>
       </c>
       <c r="G33" s="3">
-        <v>99300</v>
+        <v>41400</v>
       </c>
       <c r="H33" s="3">
-        <v>-155600</v>
+        <v>-64900</v>
       </c>
       <c r="I33" s="3">
-        <v>41700</v>
+        <v>17400</v>
       </c>
       <c r="J33" s="3">
-        <v>-3200</v>
+        <v>-1300</v>
       </c>
       <c r="K33" s="3">
         <v>25700</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>162300</v>
+        <v>67700</v>
       </c>
       <c r="E35" s="3">
-        <v>210800</v>
+        <v>87900</v>
       </c>
       <c r="F35" s="3">
-        <v>-299400</v>
+        <v>-124800</v>
       </c>
       <c r="G35" s="3">
-        <v>99300</v>
+        <v>41400</v>
       </c>
       <c r="H35" s="3">
-        <v>-155600</v>
+        <v>-64900</v>
       </c>
       <c r="I35" s="3">
-        <v>41700</v>
+        <v>17400</v>
       </c>
       <c r="J35" s="3">
-        <v>-3200</v>
+        <v>-1300</v>
       </c>
       <c r="K35" s="3">
         <v>25700</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>24700</v>
+        <v>10300</v>
       </c>
       <c r="E41" s="3">
-        <v>77900</v>
+        <v>32500</v>
       </c>
       <c r="F41" s="3">
-        <v>9000</v>
+        <v>3700</v>
       </c>
       <c r="G41" s="3">
-        <v>384100</v>
+        <v>160100</v>
       </c>
       <c r="H41" s="3">
-        <v>244600</v>
+        <v>102000</v>
       </c>
       <c r="I41" s="3">
-        <v>164300</v>
+        <v>68500</v>
       </c>
       <c r="J41" s="3">
-        <v>70300</v>
+        <v>29300</v>
       </c>
       <c r="K41" s="3">
         <v>79300</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>97400</v>
+        <v>40600</v>
       </c>
       <c r="E42" s="3">
-        <v>112500</v>
+        <v>46900</v>
       </c>
       <c r="F42" s="3">
-        <v>14700</v>
+        <v>6100</v>
       </c>
       <c r="G42" s="3">
-        <v>97000</v>
+        <v>40400</v>
       </c>
       <c r="H42" s="3">
-        <v>177500</v>
+        <v>74000</v>
       </c>
       <c r="I42" s="3">
-        <v>131900</v>
+        <v>55000</v>
       </c>
       <c r="J42" s="3">
-        <v>40400</v>
+        <v>16900</v>
       </c>
       <c r="K42" s="3">
         <v>31200</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>75300</v>
+        <v>31400</v>
       </c>
       <c r="E43" s="3">
+        <v>27700</v>
+      </c>
+      <c r="F43" s="3">
+        <v>16700</v>
+      </c>
+      <c r="G43" s="3">
         <v>66400</v>
       </c>
-      <c r="F43" s="3">
-        <v>40100</v>
-      </c>
-      <c r="G43" s="3">
-        <v>159200</v>
-      </c>
       <c r="H43" s="3">
-        <v>92800</v>
+        <v>38700</v>
       </c>
       <c r="I43" s="3">
-        <v>67600</v>
+        <v>28200</v>
       </c>
       <c r="J43" s="3">
-        <v>45000</v>
+        <v>18800</v>
       </c>
       <c r="K43" s="3">
         <v>37400</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1300</v>
+        <v>600</v>
       </c>
       <c r="E44" s="3">
-        <v>1900</v>
+        <v>800</v>
       </c>
       <c r="F44" s="3">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="G44" s="3">
-        <v>29800</v>
+        <v>12400</v>
       </c>
       <c r="H44" s="3">
-        <v>6100</v>
+        <v>2600</v>
       </c>
       <c r="I44" s="3">
-        <v>17200</v>
+        <v>7200</v>
       </c>
       <c r="J44" s="3">
-        <v>15600</v>
+        <v>6500</v>
       </c>
       <c r="K44" s="3">
         <v>9300</v>
@@ -2084,16 +2084,16 @@
         <v>0</v>
       </c>
       <c r="G45" s="3">
-        <v>204400</v>
+        <v>85200</v>
       </c>
       <c r="H45" s="3">
-        <v>50400</v>
+        <v>21000</v>
       </c>
       <c r="I45" s="3">
-        <v>41900</v>
+        <v>17500</v>
       </c>
       <c r="J45" s="3">
-        <v>13900</v>
+        <v>5800</v>
       </c>
       <c r="K45" s="3">
         <v>4800</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>198700</v>
+        <v>82900</v>
       </c>
       <c r="E46" s="3">
-        <v>258800</v>
+        <v>107900</v>
       </c>
       <c r="F46" s="3">
-        <v>64600</v>
+        <v>26900</v>
       </c>
       <c r="G46" s="3">
-        <v>874400</v>
+        <v>364600</v>
       </c>
       <c r="H46" s="3">
-        <v>571400</v>
+        <v>238300</v>
       </c>
       <c r="I46" s="3">
-        <v>422900</v>
+        <v>176300</v>
       </c>
       <c r="J46" s="3">
-        <v>185300</v>
+        <v>77300</v>
       </c>
       <c r="K46" s="3">
         <v>122300</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>123000</v>
+        <v>51300</v>
       </c>
       <c r="E47" s="3">
-        <v>130300</v>
+        <v>54300</v>
       </c>
       <c r="F47" s="3">
-        <v>75500</v>
+        <v>31500</v>
       </c>
       <c r="G47" s="3">
-        <v>429600</v>
+        <v>179100</v>
       </c>
       <c r="H47" s="3">
-        <v>188100</v>
+        <v>78400</v>
       </c>
       <c r="I47" s="3">
-        <v>159300</v>
+        <v>66400</v>
       </c>
       <c r="J47" s="3">
-        <v>37100</v>
+        <v>15500</v>
       </c>
       <c r="K47" s="3">
         <v>61100</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1650200</v>
+        <v>688000</v>
       </c>
       <c r="E48" s="3">
-        <v>1845700</v>
+        <v>769600</v>
       </c>
       <c r="F48" s="3">
-        <v>873000</v>
+        <v>364000</v>
       </c>
       <c r="G48" s="3">
-        <v>1212000</v>
+        <v>505400</v>
       </c>
       <c r="H48" s="3">
-        <v>1034200</v>
+        <v>431200</v>
       </c>
       <c r="I48" s="3">
-        <v>958000</v>
+        <v>399500</v>
       </c>
       <c r="J48" s="3">
-        <v>359600</v>
+        <v>149900</v>
       </c>
       <c r="K48" s="3">
         <v>447900</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>22500</v>
+        <v>9400</v>
       </c>
       <c r="E49" s="3">
-        <v>20600</v>
+        <v>8600</v>
       </c>
       <c r="F49" s="3">
-        <v>11100</v>
+        <v>4600</v>
       </c>
       <c r="G49" s="3">
-        <v>118100</v>
+        <v>49200</v>
       </c>
       <c r="H49" s="3">
-        <v>72500</v>
+        <v>30200</v>
       </c>
       <c r="I49" s="3">
-        <v>54600</v>
+        <v>22800</v>
       </c>
       <c r="J49" s="3">
-        <v>35100</v>
+        <v>14600</v>
       </c>
       <c r="K49" s="3">
         <v>33600</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>19500</v>
+        <v>8100</v>
       </c>
       <c r="E52" s="3">
-        <v>19000</v>
+        <v>7900</v>
       </c>
       <c r="F52" s="3">
-        <v>9700</v>
+        <v>4000</v>
       </c>
       <c r="G52" s="3">
-        <v>31900</v>
+        <v>13300</v>
       </c>
       <c r="H52" s="3">
-        <v>53600</v>
+        <v>22400</v>
       </c>
       <c r="I52" s="3">
-        <v>99000</v>
+        <v>41300</v>
       </c>
       <c r="J52" s="3">
-        <v>37300</v>
+        <v>15600</v>
       </c>
       <c r="K52" s="3">
         <v>27200</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2013900</v>
+        <v>839700</v>
       </c>
       <c r="E54" s="3">
-        <v>2274400</v>
+        <v>948300</v>
       </c>
       <c r="F54" s="3">
-        <v>1033900</v>
+        <v>431100</v>
       </c>
       <c r="G54" s="3">
-        <v>2666000</v>
+        <v>1111600</v>
       </c>
       <c r="H54" s="3">
-        <v>1919800</v>
+        <v>800500</v>
       </c>
       <c r="I54" s="3">
-        <v>1491000</v>
+        <v>621700</v>
       </c>
       <c r="J54" s="3">
-        <v>654400</v>
+        <v>272900</v>
       </c>
       <c r="K54" s="3">
         <v>549500</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>85100</v>
+        <v>35500</v>
       </c>
       <c r="E57" s="3">
-        <v>52000</v>
+        <v>21700</v>
       </c>
       <c r="F57" s="3">
-        <v>23700</v>
+        <v>9900</v>
       </c>
       <c r="G57" s="3">
-        <v>126100</v>
+        <v>52600</v>
       </c>
       <c r="H57" s="3">
-        <v>75100</v>
+        <v>31300</v>
       </c>
       <c r="I57" s="3">
-        <v>64900</v>
+        <v>27100</v>
       </c>
       <c r="J57" s="3">
-        <v>36000</v>
+        <v>15000</v>
       </c>
       <c r="K57" s="3">
         <v>31700</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>116000</v>
+        <v>48400</v>
       </c>
       <c r="E58" s="3">
-        <v>376800</v>
+        <v>157100</v>
       </c>
       <c r="F58" s="3">
-        <v>71800</v>
+        <v>29900</v>
       </c>
       <c r="G58" s="3">
-        <v>353700</v>
+        <v>147500</v>
       </c>
       <c r="H58" s="3">
-        <v>312800</v>
+        <v>130400</v>
       </c>
       <c r="I58" s="3">
-        <v>112600</v>
+        <v>47000</v>
       </c>
       <c r="J58" s="3">
-        <v>56400</v>
+        <v>23500</v>
       </c>
       <c r="K58" s="3">
         <v>63600</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>13200</v>
+        <v>5500</v>
       </c>
       <c r="E59" s="3">
-        <v>98500</v>
+        <v>41100</v>
       </c>
       <c r="F59" s="3">
-        <v>7300</v>
+        <v>3000</v>
       </c>
       <c r="G59" s="3">
-        <v>129700</v>
+        <v>54100</v>
       </c>
       <c r="H59" s="3">
-        <v>40000</v>
+        <v>16700</v>
       </c>
       <c r="I59" s="3">
-        <v>28900</v>
+        <v>12000</v>
       </c>
       <c r="J59" s="3">
-        <v>39000</v>
+        <v>16300</v>
       </c>
       <c r="K59" s="3">
         <v>29400</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>214300</v>
+        <v>89400</v>
       </c>
       <c r="E60" s="3">
-        <v>527300</v>
+        <v>219900</v>
       </c>
       <c r="F60" s="3">
-        <v>102700</v>
+        <v>42800</v>
       </c>
       <c r="G60" s="3">
-        <v>609500</v>
+        <v>254100</v>
       </c>
       <c r="H60" s="3">
-        <v>299100</v>
+        <v>124700</v>
       </c>
       <c r="I60" s="3">
-        <v>206400</v>
+        <v>86100</v>
       </c>
       <c r="J60" s="3">
-        <v>131400</v>
+        <v>54800</v>
       </c>
       <c r="K60" s="3">
         <v>124700</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>198000</v>
+        <v>82600</v>
       </c>
       <c r="E61" s="3">
-        <v>86600</v>
+        <v>36100</v>
       </c>
       <c r="F61" s="3">
-        <v>220800</v>
+        <v>92100</v>
       </c>
       <c r="G61" s="3">
-        <v>1322800</v>
+        <v>551500</v>
       </c>
       <c r="H61" s="3">
-        <v>1080000</v>
+        <v>450300</v>
       </c>
       <c r="I61" s="3">
-        <v>797100</v>
+        <v>332400</v>
       </c>
       <c r="J61" s="3">
-        <v>309900</v>
+        <v>129200</v>
       </c>
       <c r="K61" s="3">
         <v>259300</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>513800</v>
+        <v>214200</v>
       </c>
       <c r="E62" s="3">
-        <v>625000</v>
+        <v>260600</v>
       </c>
       <c r="F62" s="3">
-        <v>326400</v>
+        <v>136100</v>
       </c>
       <c r="G62" s="3">
-        <v>212400</v>
+        <v>88600</v>
       </c>
       <c r="H62" s="3">
-        <v>193500</v>
+        <v>80700</v>
       </c>
       <c r="I62" s="3">
-        <v>149300</v>
+        <v>62200</v>
       </c>
       <c r="J62" s="3">
-        <v>79200</v>
+        <v>33000</v>
       </c>
       <c r="K62" s="3">
         <v>64400</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>989300</v>
+        <v>412500</v>
       </c>
       <c r="E66" s="3">
-        <v>1305200</v>
+        <v>544200</v>
       </c>
       <c r="F66" s="3">
-        <v>746900</v>
+        <v>311400</v>
       </c>
       <c r="G66" s="3">
-        <v>2423200</v>
+        <v>1010400</v>
       </c>
       <c r="H66" s="3">
-        <v>1790000</v>
+        <v>746400</v>
       </c>
       <c r="I66" s="3">
-        <v>1317400</v>
+        <v>549300</v>
       </c>
       <c r="J66" s="3">
-        <v>581200</v>
+        <v>242300</v>
       </c>
       <c r="K66" s="3">
         <v>487700</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>406800</v>
+        <v>169600</v>
       </c>
       <c r="E72" s="3">
-        <v>351400</v>
+        <v>146500</v>
       </c>
       <c r="F72" s="3">
-        <v>75600</v>
+        <v>31500</v>
       </c>
       <c r="G72" s="3">
-        <v>120600</v>
+        <v>50300</v>
       </c>
       <c r="H72" s="3">
-        <v>48400</v>
+        <v>20200</v>
       </c>
       <c r="I72" s="3">
-        <v>116700</v>
+        <v>48700</v>
       </c>
       <c r="J72" s="3">
-        <v>68900</v>
+        <v>28700</v>
       </c>
       <c r="K72" s="3">
         <v>57500</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1024600</v>
+        <v>427200</v>
       </c>
       <c r="E76" s="3">
-        <v>969200</v>
+        <v>404100</v>
       </c>
       <c r="F76" s="3">
-        <v>286900</v>
+        <v>119600</v>
       </c>
       <c r="G76" s="3">
-        <v>242800</v>
+        <v>101200</v>
       </c>
       <c r="H76" s="3">
-        <v>129700</v>
+        <v>54100</v>
       </c>
       <c r="I76" s="3">
-        <v>173600</v>
+        <v>72400</v>
       </c>
       <c r="J76" s="3">
-        <v>73200</v>
+        <v>30500</v>
       </c>
       <c r="K76" s="3">
         <v>61900</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>162300</v>
+        <v>67700</v>
       </c>
       <c r="E81" s="3">
-        <v>210800</v>
+        <v>87900</v>
       </c>
       <c r="F81" s="3">
-        <v>-299400</v>
+        <v>-124800</v>
       </c>
       <c r="G81" s="3">
-        <v>99300</v>
+        <v>41400</v>
       </c>
       <c r="H81" s="3">
-        <v>-155600</v>
+        <v>-64900</v>
       </c>
       <c r="I81" s="3">
-        <v>41700</v>
+        <v>17400</v>
       </c>
       <c r="J81" s="3">
-        <v>-3200</v>
+        <v>-1300</v>
       </c>
       <c r="K81" s="3">
         <v>25700</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5400</v>
+        <v>2200</v>
       </c>
       <c r="E83" s="3">
-        <v>5700</v>
+        <v>2400</v>
       </c>
       <c r="F83" s="3">
-        <v>6400</v>
+        <v>2700</v>
       </c>
       <c r="G83" s="3">
-        <v>3300</v>
+        <v>1400</v>
       </c>
       <c r="H83" s="3">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="I83" s="3">
-        <v>19100</v>
+        <v>8000</v>
       </c>
       <c r="J83" s="3">
-        <v>9600</v>
+        <v>4000</v>
       </c>
       <c r="K83" s="3">
         <v>4400</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>99900</v>
+        <v>41700</v>
       </c>
       <c r="E89" s="3">
-        <v>74900</v>
+        <v>31200</v>
       </c>
       <c r="F89" s="3">
-        <v>-1441600</v>
+        <v>-601100</v>
       </c>
       <c r="G89" s="3">
-        <v>216900</v>
+        <v>90400</v>
       </c>
       <c r="H89" s="3">
-        <v>114900</v>
+        <v>47900</v>
       </c>
       <c r="I89" s="3">
-        <v>40400</v>
+        <v>16900</v>
       </c>
       <c r="J89" s="3">
-        <v>25600</v>
+        <v>10700</v>
       </c>
       <c r="K89" s="3">
         <v>11800</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-19000</v>
+        <v>-7900</v>
       </c>
       <c r="E91" s="3">
-        <v>-39500</v>
+        <v>-16500</v>
       </c>
       <c r="F91" s="3">
-        <v>-13100</v>
+        <v>-5400</v>
       </c>
       <c r="G91" s="3">
-        <v>-27400</v>
+        <v>-11400</v>
       </c>
       <c r="H91" s="3">
-        <v>-18800</v>
+        <v>-7800</v>
       </c>
       <c r="I91" s="3">
-        <v>-26400</v>
+        <v>-11000</v>
       </c>
       <c r="J91" s="3">
-        <v>-11500</v>
+        <v>-4800</v>
       </c>
       <c r="K91" s="3">
         <v>-3900</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>74800</v>
+        <v>31200</v>
       </c>
       <c r="E94" s="3">
-        <v>68300</v>
+        <v>28500</v>
       </c>
       <c r="F94" s="3">
-        <v>673900</v>
+        <v>281000</v>
       </c>
       <c r="G94" s="3">
-        <v>317800</v>
+        <v>132500</v>
       </c>
       <c r="H94" s="3">
-        <v>47600</v>
+        <v>19800</v>
       </c>
       <c r="I94" s="3">
-        <v>-60500</v>
+        <v>-25200</v>
       </c>
       <c r="J94" s="3">
-        <v>-5900</v>
+        <v>-2400</v>
       </c>
       <c r="K94" s="3">
         <v>23500</v>
@@ -3994,13 +3994,13 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-91400</v>
+        <v>-38100</v>
       </c>
       <c r="E96" s="3">
-        <v>-1100</v>
+        <v>-500</v>
       </c>
       <c r="F96" s="3">
-        <v>-25900</v>
+        <v>-10800</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -4009,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-7300</v>
+        <v>-3000</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-229600</v>
+        <v>-95700</v>
       </c>
       <c r="E100" s="3">
-        <v>-83400</v>
+        <v>-34800</v>
       </c>
       <c r="F100" s="3">
-        <v>-483400</v>
+        <v>-201600</v>
       </c>
       <c r="G100" s="3">
-        <v>-565100</v>
+        <v>-235600</v>
       </c>
       <c r="H100" s="3">
-        <v>-118000</v>
+        <v>-49200</v>
       </c>
       <c r="I100" s="3">
-        <v>-12200</v>
+        <v>-5100</v>
       </c>
       <c r="J100" s="3">
-        <v>4300</v>
+        <v>1800</v>
       </c>
       <c r="K100" s="3">
         <v>-11300</v>
@@ -4204,25 +4204,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="E101" s="3">
-        <v>-1200</v>
+        <v>-500</v>
       </c>
       <c r="F101" s="3">
-        <v>-87300</v>
+        <v>-36400</v>
       </c>
       <c r="G101" s="3">
-        <v>60900</v>
+        <v>25400</v>
       </c>
       <c r="H101" s="3">
-        <v>-28800</v>
+        <v>-12000</v>
       </c>
       <c r="I101" s="3">
-        <v>56500</v>
+        <v>23600</v>
       </c>
       <c r="J101" s="3">
-        <v>7400</v>
+        <v>3100</v>
       </c>
       <c r="K101" s="3">
         <v>14600</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-53200</v>
+        <v>-22200</v>
       </c>
       <c r="E102" s="3">
-        <v>58600</v>
+        <v>24400</v>
       </c>
       <c r="F102" s="3">
-        <v>-1338500</v>
+        <v>-558100</v>
       </c>
       <c r="G102" s="3">
-        <v>30400</v>
+        <v>12700</v>
       </c>
       <c r="H102" s="3">
-        <v>15800</v>
+        <v>6600</v>
       </c>
       <c r="I102" s="3">
-        <v>24300</v>
+        <v>10100</v>
       </c>
       <c r="J102" s="3">
-        <v>31500</v>
+        <v>13200</v>
       </c>
       <c r="K102" s="3">
         <v>38600</v>

--- a/AAII_Financials/Yearly/IRS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IRS_YR_FIN.xlsx
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>105400</v>
+        <v>99100</v>
       </c>
       <c r="E8" s="3">
-        <v>81600</v>
+        <v>76800</v>
       </c>
       <c r="F8" s="3">
-        <v>54100</v>
+        <v>50900</v>
       </c>
       <c r="G8" s="3">
-        <v>41100</v>
+        <v>38700</v>
       </c>
       <c r="H8" s="3">
-        <v>33000</v>
+        <v>31100</v>
       </c>
       <c r="I8" s="3">
-        <v>69400</v>
+        <v>65300</v>
       </c>
       <c r="J8" s="3">
-        <v>70400</v>
+        <v>66200</v>
       </c>
       <c r="K8" s="3">
         <v>36900</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>36300</v>
+        <v>34200</v>
       </c>
       <c r="E9" s="3">
-        <v>30900</v>
+        <v>29100</v>
       </c>
       <c r="F9" s="3">
-        <v>28200</v>
+        <v>26500</v>
       </c>
       <c r="G9" s="3">
-        <v>17700</v>
+        <v>16700</v>
       </c>
       <c r="H9" s="3">
-        <v>12300</v>
+        <v>11600</v>
       </c>
       <c r="I9" s="3">
-        <v>40900</v>
+        <v>38500</v>
       </c>
       <c r="J9" s="3">
-        <v>98100</v>
+        <v>92200</v>
       </c>
       <c r="K9" s="3">
         <v>127200</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>69000</v>
+        <v>64900</v>
       </c>
       <c r="E10" s="3">
-        <v>50700</v>
+        <v>47700</v>
       </c>
       <c r="F10" s="3">
-        <v>26000</v>
+        <v>24400</v>
       </c>
       <c r="G10" s="3">
-        <v>23400</v>
+        <v>22000</v>
       </c>
       <c r="H10" s="3">
-        <v>20700</v>
+        <v>19500</v>
       </c>
       <c r="I10" s="3">
-        <v>28500</v>
+        <v>26800</v>
       </c>
       <c r="J10" s="3">
-        <v>-27600</v>
+        <v>-26000</v>
       </c>
       <c r="K10" s="3">
         <v>-90300</v>
@@ -951,7 +951,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>8800</v>
+        <v>8300</v>
       </c>
       <c r="E14" s="3">
         <v>700</v>
@@ -960,13 +960,13 @@
         <v>200</v>
       </c>
       <c r="G14" s="3">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="H14" s="3">
         <v>400</v>
       </c>
       <c r="I14" s="3">
-        <v>-1600</v>
+        <v>-1500</v>
       </c>
       <c r="J14" s="3">
         <v>500</v>
@@ -993,13 +993,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="3">
         <v>700</v>
       </c>
-      <c r="E15" s="3">
-        <v>800</v>
-      </c>
       <c r="F15" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="G15" s="3">
         <v>700</v>
@@ -1008,10 +1008,10 @@
         <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>3200</v>
+        <v>3000</v>
       </c>
       <c r="J15" s="3">
-        <v>4100</v>
+        <v>3900</v>
       </c>
       <c r="K15" s="3">
         <v>2300</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>136200</v>
+        <v>128100</v>
       </c>
       <c r="E17" s="3">
-        <v>15100</v>
+        <v>14200</v>
       </c>
       <c r="F17" s="3">
-        <v>79000</v>
+        <v>74300</v>
       </c>
       <c r="G17" s="3">
-        <v>-71200</v>
+        <v>-67000</v>
       </c>
       <c r="H17" s="3">
-        <v>88300</v>
+        <v>83100</v>
       </c>
       <c r="I17" s="3">
-        <v>36900</v>
+        <v>34700</v>
       </c>
       <c r="J17" s="3">
-        <v>66900</v>
+        <v>62900</v>
       </c>
       <c r="K17" s="3">
         <v>-20100</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-30800</v>
+        <v>-29000</v>
       </c>
       <c r="E18" s="3">
-        <v>66600</v>
+        <v>62600</v>
       </c>
       <c r="F18" s="3">
-        <v>-24800</v>
+        <v>-23300</v>
       </c>
       <c r="G18" s="3">
-        <v>112300</v>
+        <v>105700</v>
       </c>
       <c r="H18" s="3">
-        <v>-55300</v>
+        <v>-52000</v>
       </c>
       <c r="I18" s="3">
-        <v>32500</v>
+        <v>30500</v>
       </c>
       <c r="J18" s="3">
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="K18" s="3">
         <v>57100</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>35700</v>
+        <v>33600</v>
       </c>
       <c r="E20" s="3">
-        <v>50300</v>
+        <v>47400</v>
       </c>
       <c r="F20" s="3">
-        <v>36300</v>
+        <v>34100</v>
       </c>
       <c r="G20" s="3">
-        <v>13000</v>
+        <v>12200</v>
       </c>
       <c r="H20" s="3">
-        <v>-10000</v>
+        <v>-9400</v>
       </c>
       <c r="I20" s="3">
-        <v>-20600</v>
+        <v>-19300</v>
       </c>
       <c r="J20" s="3">
-        <v>6900</v>
+        <v>6500</v>
       </c>
       <c r="K20" s="3">
         <v>-7500</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7100</v>
+        <v>6700</v>
       </c>
       <c r="E21" s="3">
-        <v>119300</v>
+        <v>112200</v>
       </c>
       <c r="F21" s="3">
-        <v>14100</v>
+        <v>13300</v>
       </c>
       <c r="G21" s="3">
-        <v>126700</v>
+        <v>119200</v>
       </c>
       <c r="H21" s="3">
-        <v>-64600</v>
+        <v>-60800</v>
       </c>
       <c r="I21" s="3">
-        <v>19900</v>
+        <v>18700</v>
       </c>
       <c r="J21" s="3">
-        <v>14500</v>
+        <v>13600</v>
       </c>
       <c r="K21" s="3">
         <v>54000</v>
@@ -1236,25 +1236,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>14300</v>
+        <v>13500</v>
       </c>
       <c r="E22" s="3">
-        <v>21100</v>
+        <v>19800</v>
       </c>
       <c r="F22" s="3">
-        <v>40600</v>
+        <v>38200</v>
       </c>
       <c r="G22" s="3">
-        <v>27300</v>
+        <v>25600</v>
       </c>
       <c r="H22" s="3">
-        <v>7900</v>
+        <v>7400</v>
       </c>
       <c r="I22" s="3">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="J22" s="3">
-        <v>15600</v>
+        <v>14600</v>
       </c>
       <c r="K22" s="3">
         <v>6700</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-9400</v>
+        <v>-8900</v>
       </c>
       <c r="E23" s="3">
-        <v>95800</v>
+        <v>90100</v>
       </c>
       <c r="F23" s="3">
-        <v>-29200</v>
+        <v>-27400</v>
       </c>
       <c r="G23" s="3">
-        <v>98000</v>
+        <v>92200</v>
       </c>
       <c r="H23" s="3">
-        <v>-73200</v>
+        <v>-68800</v>
       </c>
       <c r="I23" s="3">
-        <v>-4000</v>
+        <v>-3800</v>
       </c>
       <c r="J23" s="3">
-        <v>-5100</v>
+        <v>-4800</v>
       </c>
       <c r="K23" s="3">
         <v>42900</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-78000</v>
+        <v>-73300</v>
       </c>
       <c r="E24" s="3">
-        <v>7000</v>
+        <v>6600</v>
       </c>
       <c r="F24" s="3">
-        <v>90400</v>
+        <v>85000</v>
       </c>
       <c r="G24" s="3">
-        <v>19500</v>
+        <v>18300</v>
       </c>
       <c r="H24" s="3">
-        <v>-8000</v>
+        <v>-7500</v>
       </c>
       <c r="I24" s="3">
-        <v>-7400</v>
+        <v>-7000</v>
       </c>
       <c r="J24" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="K24" s="3">
         <v>18100</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>68600</v>
+        <v>64500</v>
       </c>
       <c r="E26" s="3">
-        <v>88800</v>
+        <v>83500</v>
       </c>
       <c r="F26" s="3">
-        <v>-119600</v>
+        <v>-112500</v>
       </c>
       <c r="G26" s="3">
-        <v>78600</v>
+        <v>73900</v>
       </c>
       <c r="H26" s="3">
-        <v>-65200</v>
+        <v>-61300</v>
       </c>
       <c r="I26" s="3">
-        <v>3400</v>
+        <v>3200</v>
       </c>
       <c r="J26" s="3">
-        <v>-6800</v>
+        <v>-6400</v>
       </c>
       <c r="K26" s="3">
         <v>24800</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>67700</v>
+        <v>63700</v>
       </c>
       <c r="E27" s="3">
-        <v>87900</v>
+        <v>82700</v>
       </c>
       <c r="F27" s="3">
-        <v>-87600</v>
+        <v>-82400</v>
       </c>
       <c r="G27" s="3">
-        <v>51000</v>
+        <v>48000</v>
       </c>
       <c r="H27" s="3">
-        <v>-62100</v>
+        <v>-58400</v>
       </c>
       <c r="I27" s="3">
-        <v>-6700</v>
+        <v>-6300</v>
       </c>
       <c r="J27" s="3">
-        <v>-11700</v>
+        <v>-11100</v>
       </c>
       <c r="K27" s="3">
         <v>23300</v>
@@ -1536,19 +1536,19 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-37200</v>
+        <v>-35000</v>
       </c>
       <c r="G29" s="3">
-        <v>-9600</v>
+        <v>-9000</v>
       </c>
       <c r="H29" s="3">
-        <v>-2800</v>
+        <v>-2600</v>
       </c>
       <c r="I29" s="3">
-        <v>24000</v>
+        <v>22600</v>
       </c>
       <c r="J29" s="3">
-        <v>10400</v>
+        <v>9800</v>
       </c>
       <c r="K29" s="3">
         <v>2300</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-35700</v>
+        <v>-33600</v>
       </c>
       <c r="E32" s="3">
-        <v>-50300</v>
+        <v>-47400</v>
       </c>
       <c r="F32" s="3">
-        <v>-36300</v>
+        <v>-34100</v>
       </c>
       <c r="G32" s="3">
-        <v>-13000</v>
+        <v>-12200</v>
       </c>
       <c r="H32" s="3">
-        <v>10000</v>
+        <v>9400</v>
       </c>
       <c r="I32" s="3">
-        <v>20600</v>
+        <v>19300</v>
       </c>
       <c r="J32" s="3">
-        <v>-6900</v>
+        <v>-6500</v>
       </c>
       <c r="K32" s="3">
         <v>7500</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>67700</v>
+        <v>63700</v>
       </c>
       <c r="E33" s="3">
-        <v>87900</v>
+        <v>82700</v>
       </c>
       <c r="F33" s="3">
-        <v>-124800</v>
+        <v>-117400</v>
       </c>
       <c r="G33" s="3">
-        <v>41400</v>
+        <v>39000</v>
       </c>
       <c r="H33" s="3">
-        <v>-64900</v>
+        <v>-61000</v>
       </c>
       <c r="I33" s="3">
-        <v>17400</v>
+        <v>16300</v>
       </c>
       <c r="J33" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="K33" s="3">
         <v>25700</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>67700</v>
+        <v>63700</v>
       </c>
       <c r="E35" s="3">
-        <v>87900</v>
+        <v>82700</v>
       </c>
       <c r="F35" s="3">
-        <v>-124800</v>
+        <v>-117400</v>
       </c>
       <c r="G35" s="3">
-        <v>41400</v>
+        <v>39000</v>
       </c>
       <c r="H35" s="3">
-        <v>-64900</v>
+        <v>-61000</v>
       </c>
       <c r="I35" s="3">
-        <v>17400</v>
+        <v>16300</v>
       </c>
       <c r="J35" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="K35" s="3">
         <v>25700</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>10300</v>
+        <v>9700</v>
       </c>
       <c r="E41" s="3">
-        <v>32500</v>
+        <v>30600</v>
       </c>
       <c r="F41" s="3">
-        <v>3700</v>
+        <v>3500</v>
       </c>
       <c r="G41" s="3">
-        <v>160100</v>
+        <v>150600</v>
       </c>
       <c r="H41" s="3">
-        <v>102000</v>
+        <v>96000</v>
       </c>
       <c r="I41" s="3">
-        <v>68500</v>
+        <v>64400</v>
       </c>
       <c r="J41" s="3">
-        <v>29300</v>
+        <v>27600</v>
       </c>
       <c r="K41" s="3">
         <v>79300</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>40600</v>
+        <v>38200</v>
       </c>
       <c r="E42" s="3">
-        <v>46900</v>
+        <v>44100</v>
       </c>
       <c r="F42" s="3">
-        <v>6100</v>
+        <v>5800</v>
       </c>
       <c r="G42" s="3">
-        <v>40400</v>
+        <v>38000</v>
       </c>
       <c r="H42" s="3">
-        <v>74000</v>
+        <v>69600</v>
       </c>
       <c r="I42" s="3">
-        <v>55000</v>
+        <v>51700</v>
       </c>
       <c r="J42" s="3">
-        <v>16900</v>
+        <v>15900</v>
       </c>
       <c r="K42" s="3">
         <v>31200</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>31400</v>
+        <v>29500</v>
       </c>
       <c r="E43" s="3">
-        <v>27700</v>
+        <v>26000</v>
       </c>
       <c r="F43" s="3">
-        <v>16700</v>
+        <v>15700</v>
       </c>
       <c r="G43" s="3">
-        <v>66400</v>
+        <v>62400</v>
       </c>
       <c r="H43" s="3">
-        <v>38700</v>
+        <v>36400</v>
       </c>
       <c r="I43" s="3">
-        <v>28200</v>
+        <v>26500</v>
       </c>
       <c r="J43" s="3">
-        <v>18800</v>
+        <v>17700</v>
       </c>
       <c r="K43" s="3">
         <v>37400</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E44" s="3">
         <v>800</v>
       </c>
       <c r="F44" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G44" s="3">
-        <v>12400</v>
+        <v>11700</v>
       </c>
       <c r="H44" s="3">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="I44" s="3">
-        <v>7200</v>
+        <v>6700</v>
       </c>
       <c r="J44" s="3">
-        <v>6500</v>
+        <v>6100</v>
       </c>
       <c r="K44" s="3">
         <v>9300</v>
@@ -2084,16 +2084,16 @@
         <v>0</v>
       </c>
       <c r="G45" s="3">
-        <v>85200</v>
+        <v>80200</v>
       </c>
       <c r="H45" s="3">
-        <v>21000</v>
+        <v>19800</v>
       </c>
       <c r="I45" s="3">
-        <v>17500</v>
+        <v>16400</v>
       </c>
       <c r="J45" s="3">
-        <v>5800</v>
+        <v>5500</v>
       </c>
       <c r="K45" s="3">
         <v>4800</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>82900</v>
+        <v>78000</v>
       </c>
       <c r="E46" s="3">
-        <v>107900</v>
+        <v>101500</v>
       </c>
       <c r="F46" s="3">
-        <v>26900</v>
+        <v>25300</v>
       </c>
       <c r="G46" s="3">
-        <v>364600</v>
+        <v>343000</v>
       </c>
       <c r="H46" s="3">
-        <v>238300</v>
+        <v>224100</v>
       </c>
       <c r="I46" s="3">
-        <v>176300</v>
+        <v>165900</v>
       </c>
       <c r="J46" s="3">
-        <v>77300</v>
+        <v>72700</v>
       </c>
       <c r="K46" s="3">
         <v>122300</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>51300</v>
+        <v>48200</v>
       </c>
       <c r="E47" s="3">
-        <v>54300</v>
+        <v>51100</v>
       </c>
       <c r="F47" s="3">
-        <v>31500</v>
+        <v>29600</v>
       </c>
       <c r="G47" s="3">
-        <v>179100</v>
+        <v>168500</v>
       </c>
       <c r="H47" s="3">
-        <v>78400</v>
+        <v>73800</v>
       </c>
       <c r="I47" s="3">
-        <v>66400</v>
+        <v>62500</v>
       </c>
       <c r="J47" s="3">
-        <v>15500</v>
+        <v>14500</v>
       </c>
       <c r="K47" s="3">
         <v>61100</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>688000</v>
+        <v>647200</v>
       </c>
       <c r="E48" s="3">
-        <v>769600</v>
+        <v>723900</v>
       </c>
       <c r="F48" s="3">
-        <v>364000</v>
+        <v>342400</v>
       </c>
       <c r="G48" s="3">
-        <v>505400</v>
+        <v>475400</v>
       </c>
       <c r="H48" s="3">
-        <v>431200</v>
+        <v>405600</v>
       </c>
       <c r="I48" s="3">
-        <v>399500</v>
+        <v>375800</v>
       </c>
       <c r="J48" s="3">
-        <v>149900</v>
+        <v>141000</v>
       </c>
       <c r="K48" s="3">
         <v>447900</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9400</v>
+        <v>8800</v>
       </c>
       <c r="E49" s="3">
-        <v>8600</v>
+        <v>8100</v>
       </c>
       <c r="F49" s="3">
-        <v>4600</v>
+        <v>4400</v>
       </c>
       <c r="G49" s="3">
-        <v>49200</v>
+        <v>46300</v>
       </c>
       <c r="H49" s="3">
-        <v>30200</v>
+        <v>28400</v>
       </c>
       <c r="I49" s="3">
-        <v>22800</v>
+        <v>21400</v>
       </c>
       <c r="J49" s="3">
-        <v>14600</v>
+        <v>13700</v>
       </c>
       <c r="K49" s="3">
         <v>33600</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>8100</v>
+        <v>7700</v>
       </c>
       <c r="E52" s="3">
-        <v>7900</v>
+        <v>7500</v>
       </c>
       <c r="F52" s="3">
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="G52" s="3">
-        <v>13300</v>
+        <v>12500</v>
       </c>
       <c r="H52" s="3">
-        <v>22400</v>
+        <v>21000</v>
       </c>
       <c r="I52" s="3">
-        <v>41300</v>
+        <v>38800</v>
       </c>
       <c r="J52" s="3">
-        <v>15600</v>
+        <v>14600</v>
       </c>
       <c r="K52" s="3">
         <v>27200</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>839700</v>
+        <v>789900</v>
       </c>
       <c r="E54" s="3">
-        <v>948300</v>
+        <v>892100</v>
       </c>
       <c r="F54" s="3">
-        <v>431100</v>
+        <v>405500</v>
       </c>
       <c r="G54" s="3">
-        <v>1111600</v>
+        <v>1045700</v>
       </c>
       <c r="H54" s="3">
-        <v>800500</v>
+        <v>753000</v>
       </c>
       <c r="I54" s="3">
-        <v>621700</v>
+        <v>584800</v>
       </c>
       <c r="J54" s="3">
-        <v>272900</v>
+        <v>256700</v>
       </c>
       <c r="K54" s="3">
         <v>549500</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>35500</v>
+        <v>33400</v>
       </c>
       <c r="E57" s="3">
-        <v>21700</v>
+        <v>20400</v>
       </c>
       <c r="F57" s="3">
-        <v>9900</v>
+        <v>9300</v>
       </c>
       <c r="G57" s="3">
-        <v>52600</v>
+        <v>49500</v>
       </c>
       <c r="H57" s="3">
-        <v>31300</v>
+        <v>29400</v>
       </c>
       <c r="I57" s="3">
-        <v>27100</v>
+        <v>25400</v>
       </c>
       <c r="J57" s="3">
-        <v>15000</v>
+        <v>14100</v>
       </c>
       <c r="K57" s="3">
         <v>31700</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>48400</v>
+        <v>45500</v>
       </c>
       <c r="E58" s="3">
-        <v>157100</v>
+        <v>147800</v>
       </c>
       <c r="F58" s="3">
-        <v>29900</v>
+        <v>28100</v>
       </c>
       <c r="G58" s="3">
-        <v>147500</v>
+        <v>138700</v>
       </c>
       <c r="H58" s="3">
-        <v>130400</v>
+        <v>122700</v>
       </c>
       <c r="I58" s="3">
-        <v>47000</v>
+        <v>44200</v>
       </c>
       <c r="J58" s="3">
-        <v>23500</v>
+        <v>22100</v>
       </c>
       <c r="K58" s="3">
         <v>63600</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5500</v>
+        <v>5200</v>
       </c>
       <c r="E59" s="3">
-        <v>41100</v>
+        <v>38600</v>
       </c>
       <c r="F59" s="3">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="G59" s="3">
-        <v>54100</v>
+        <v>50900</v>
       </c>
       <c r="H59" s="3">
-        <v>16700</v>
+        <v>15700</v>
       </c>
       <c r="I59" s="3">
-        <v>12000</v>
+        <v>11300</v>
       </c>
       <c r="J59" s="3">
-        <v>16300</v>
+        <v>15300</v>
       </c>
       <c r="K59" s="3">
         <v>29400</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>89400</v>
+        <v>84100</v>
       </c>
       <c r="E60" s="3">
-        <v>219900</v>
+        <v>206800</v>
       </c>
       <c r="F60" s="3">
-        <v>42800</v>
+        <v>40300</v>
       </c>
       <c r="G60" s="3">
-        <v>254100</v>
+        <v>239100</v>
       </c>
       <c r="H60" s="3">
-        <v>124700</v>
+        <v>117300</v>
       </c>
       <c r="I60" s="3">
-        <v>86100</v>
+        <v>81000</v>
       </c>
       <c r="J60" s="3">
-        <v>54800</v>
+        <v>51500</v>
       </c>
       <c r="K60" s="3">
         <v>124700</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>82600</v>
+        <v>77700</v>
       </c>
       <c r="E61" s="3">
-        <v>36100</v>
+        <v>34000</v>
       </c>
       <c r="F61" s="3">
-        <v>92100</v>
+        <v>86600</v>
       </c>
       <c r="G61" s="3">
-        <v>551500</v>
+        <v>518800</v>
       </c>
       <c r="H61" s="3">
-        <v>450300</v>
+        <v>423600</v>
       </c>
       <c r="I61" s="3">
-        <v>332400</v>
+        <v>312600</v>
       </c>
       <c r="J61" s="3">
-        <v>129200</v>
+        <v>121500</v>
       </c>
       <c r="K61" s="3">
         <v>259300</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>214200</v>
+        <v>201500</v>
       </c>
       <c r="E62" s="3">
-        <v>260600</v>
+        <v>245100</v>
       </c>
       <c r="F62" s="3">
-        <v>136100</v>
+        <v>128000</v>
       </c>
       <c r="G62" s="3">
-        <v>88600</v>
+        <v>83300</v>
       </c>
       <c r="H62" s="3">
-        <v>80700</v>
+        <v>75900</v>
       </c>
       <c r="I62" s="3">
-        <v>62200</v>
+        <v>58600</v>
       </c>
       <c r="J62" s="3">
-        <v>33000</v>
+        <v>31100</v>
       </c>
       <c r="K62" s="3">
         <v>64400</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>412500</v>
+        <v>388000</v>
       </c>
       <c r="E66" s="3">
-        <v>544200</v>
+        <v>511900</v>
       </c>
       <c r="F66" s="3">
-        <v>311400</v>
+        <v>293000</v>
       </c>
       <c r="G66" s="3">
-        <v>1010400</v>
+        <v>950400</v>
       </c>
       <c r="H66" s="3">
-        <v>746400</v>
+        <v>702100</v>
       </c>
       <c r="I66" s="3">
-        <v>549300</v>
+        <v>516700</v>
       </c>
       <c r="J66" s="3">
-        <v>242300</v>
+        <v>228000</v>
       </c>
       <c r="K66" s="3">
         <v>487700</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>169600</v>
+        <v>159500</v>
       </c>
       <c r="E72" s="3">
-        <v>146500</v>
+        <v>137800</v>
       </c>
       <c r="F72" s="3">
-        <v>31500</v>
+        <v>29700</v>
       </c>
       <c r="G72" s="3">
-        <v>50300</v>
+        <v>47300</v>
       </c>
       <c r="H72" s="3">
-        <v>20200</v>
+        <v>19000</v>
       </c>
       <c r="I72" s="3">
-        <v>48700</v>
+        <v>45800</v>
       </c>
       <c r="J72" s="3">
-        <v>28700</v>
+        <v>27000</v>
       </c>
       <c r="K72" s="3">
         <v>57500</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>427200</v>
+        <v>401900</v>
       </c>
       <c r="E76" s="3">
-        <v>404100</v>
+        <v>380100</v>
       </c>
       <c r="F76" s="3">
-        <v>119600</v>
+        <v>112500</v>
       </c>
       <c r="G76" s="3">
-        <v>101200</v>
+        <v>95200</v>
       </c>
       <c r="H76" s="3">
-        <v>54100</v>
+        <v>50900</v>
       </c>
       <c r="I76" s="3">
-        <v>72400</v>
+        <v>68100</v>
       </c>
       <c r="J76" s="3">
-        <v>30500</v>
+        <v>28700</v>
       </c>
       <c r="K76" s="3">
         <v>61900</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>67700</v>
+        <v>63700</v>
       </c>
       <c r="E81" s="3">
-        <v>87900</v>
+        <v>82700</v>
       </c>
       <c r="F81" s="3">
-        <v>-124800</v>
+        <v>-117400</v>
       </c>
       <c r="G81" s="3">
-        <v>41400</v>
+        <v>39000</v>
       </c>
       <c r="H81" s="3">
-        <v>-64900</v>
+        <v>-61000</v>
       </c>
       <c r="I81" s="3">
-        <v>17400</v>
+        <v>16300</v>
       </c>
       <c r="J81" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="K81" s="3">
         <v>25700</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E83" s="3">
         <v>2200</v>
       </c>
-      <c r="E83" s="3">
-        <v>2400</v>
-      </c>
       <c r="F83" s="3">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="G83" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="H83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="I83" s="3">
-        <v>8000</v>
+        <v>7500</v>
       </c>
       <c r="J83" s="3">
-        <v>4000</v>
+        <v>3700</v>
       </c>
       <c r="K83" s="3">
         <v>4400</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>41700</v>
+        <v>39200</v>
       </c>
       <c r="E89" s="3">
-        <v>31200</v>
+        <v>29400</v>
       </c>
       <c r="F89" s="3">
-        <v>-601100</v>
+        <v>-565400</v>
       </c>
       <c r="G89" s="3">
-        <v>90400</v>
+        <v>85100</v>
       </c>
       <c r="H89" s="3">
-        <v>47900</v>
+        <v>45100</v>
       </c>
       <c r="I89" s="3">
-        <v>16900</v>
+        <v>15900</v>
       </c>
       <c r="J89" s="3">
-        <v>10700</v>
+        <v>10100</v>
       </c>
       <c r="K89" s="3">
         <v>11800</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-7900</v>
+        <v>-7400</v>
       </c>
       <c r="E91" s="3">
-        <v>-16500</v>
+        <v>-15500</v>
       </c>
       <c r="F91" s="3">
-        <v>-5400</v>
+        <v>-5100</v>
       </c>
       <c r="G91" s="3">
-        <v>-11400</v>
+        <v>-10700</v>
       </c>
       <c r="H91" s="3">
-        <v>-7800</v>
+        <v>-7400</v>
       </c>
       <c r="I91" s="3">
-        <v>-11000</v>
+        <v>-10300</v>
       </c>
       <c r="J91" s="3">
-        <v>-4800</v>
+        <v>-4500</v>
       </c>
       <c r="K91" s="3">
         <v>-3900</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>31200</v>
+        <v>29400</v>
       </c>
       <c r="E94" s="3">
-        <v>28500</v>
+        <v>26800</v>
       </c>
       <c r="F94" s="3">
-        <v>281000</v>
+        <v>264300</v>
       </c>
       <c r="G94" s="3">
-        <v>132500</v>
+        <v>124700</v>
       </c>
       <c r="H94" s="3">
-        <v>19800</v>
+        <v>18700</v>
       </c>
       <c r="I94" s="3">
-        <v>-25200</v>
+        <v>-23700</v>
       </c>
       <c r="J94" s="3">
-        <v>-2400</v>
+        <v>-2300</v>
       </c>
       <c r="K94" s="3">
         <v>23500</v>
@@ -3994,13 +3994,13 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-38100</v>
+        <v>-35800</v>
       </c>
       <c r="E96" s="3">
-        <v>-500</v>
+        <v>-400</v>
       </c>
       <c r="F96" s="3">
-        <v>-10800</v>
+        <v>-10200</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -4009,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-3000</v>
+        <v>-2900</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-95700</v>
+        <v>-90000</v>
       </c>
       <c r="E100" s="3">
-        <v>-34800</v>
+        <v>-32700</v>
       </c>
       <c r="F100" s="3">
-        <v>-201600</v>
+        <v>-189600</v>
       </c>
       <c r="G100" s="3">
-        <v>-235600</v>
+        <v>-221700</v>
       </c>
       <c r="H100" s="3">
-        <v>-49200</v>
+        <v>-46300</v>
       </c>
       <c r="I100" s="3">
-        <v>-5100</v>
+        <v>-4800</v>
       </c>
       <c r="J100" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="K100" s="3">
         <v>-11300</v>
@@ -4204,25 +4204,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E101" s="3">
         <v>-500</v>
       </c>
       <c r="F101" s="3">
-        <v>-36400</v>
+        <v>-34200</v>
       </c>
       <c r="G101" s="3">
-        <v>25400</v>
+        <v>23900</v>
       </c>
       <c r="H101" s="3">
-        <v>-12000</v>
+        <v>-11300</v>
       </c>
       <c r="I101" s="3">
-        <v>23600</v>
+        <v>22200</v>
       </c>
       <c r="J101" s="3">
-        <v>3100</v>
+        <v>2900</v>
       </c>
       <c r="K101" s="3">
         <v>14600</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-22200</v>
+        <v>-20900</v>
       </c>
       <c r="E102" s="3">
-        <v>24400</v>
+        <v>23000</v>
       </c>
       <c r="F102" s="3">
-        <v>-558100</v>
+        <v>-525000</v>
       </c>
       <c r="G102" s="3">
-        <v>12700</v>
+        <v>11900</v>
       </c>
       <c r="H102" s="3">
-        <v>6600</v>
+        <v>6200</v>
       </c>
       <c r="I102" s="3">
-        <v>10100</v>
+        <v>9500</v>
       </c>
       <c r="J102" s="3">
-        <v>13200</v>
+        <v>12400</v>
       </c>
       <c r="K102" s="3">
         <v>38600</v>

--- a/AAII_Financials/Yearly/IRS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IRS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>IRS</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44742</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44377</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44012</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43646</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43281</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42916</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42551</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42185</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41820</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41455</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41090</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>99100</v>
+        <v>341700</v>
       </c>
       <c r="E8" s="3">
-        <v>76800</v>
+        <v>92900</v>
       </c>
       <c r="F8" s="3">
-        <v>50900</v>
+        <v>71900</v>
       </c>
       <c r="G8" s="3">
-        <v>38700</v>
+        <v>47700</v>
       </c>
       <c r="H8" s="3">
-        <v>31100</v>
+        <v>36300</v>
       </c>
       <c r="I8" s="3">
-        <v>65300</v>
+        <v>29100</v>
       </c>
       <c r="J8" s="3">
+        <v>61200</v>
+      </c>
+      <c r="K8" s="3">
         <v>66200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>36900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>24800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>28200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>29700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>41100</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>34200</v>
+        <v>113600</v>
       </c>
       <c r="E9" s="3">
-        <v>29100</v>
+        <v>32000</v>
       </c>
       <c r="F9" s="3">
-        <v>26500</v>
+        <v>27200</v>
       </c>
       <c r="G9" s="3">
-        <v>16700</v>
+        <v>24800</v>
       </c>
       <c r="H9" s="3">
-        <v>11600</v>
+        <v>15600</v>
       </c>
       <c r="I9" s="3">
-        <v>38500</v>
+        <v>10900</v>
       </c>
       <c r="J9" s="3">
+        <v>36000</v>
+      </c>
+      <c r="K9" s="3">
         <v>92200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>127200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>29500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>39400</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>64900</v>
+        <v>228100</v>
       </c>
       <c r="E10" s="3">
-        <v>47700</v>
+        <v>60800</v>
       </c>
       <c r="F10" s="3">
-        <v>24400</v>
+        <v>44700</v>
       </c>
       <c r="G10" s="3">
-        <v>22000</v>
+        <v>22900</v>
       </c>
       <c r="H10" s="3">
-        <v>19500</v>
+        <v>20600</v>
       </c>
       <c r="I10" s="3">
-        <v>26800</v>
+        <v>18200</v>
       </c>
       <c r="J10" s="3">
+        <v>25100</v>
+      </c>
+      <c r="K10" s="3">
         <v>-26000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-90300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1600</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,93 +960,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="E14" s="3">
-        <v>700</v>
+        <v>7800</v>
       </c>
       <c r="F14" s="3">
+        <v>600</v>
+      </c>
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="G14" s="3">
-        <v>3000</v>
-      </c>
       <c r="H14" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I14" s="3">
         <v>400</v>
       </c>
-      <c r="I14" s="3">
-        <v>-1500</v>
-      </c>
       <c r="J14" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K14" s="3">
         <v>500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-100</v>
-      </c>
-      <c r="L14" s="3">
-        <v>200</v>
       </c>
       <c r="M14" s="3">
         <v>200</v>
       </c>
       <c r="N14" s="3">
+        <v>200</v>
+      </c>
+      <c r="O14" s="3">
         <v>-1800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E15" s="3">
         <v>600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>700</v>
       </c>
-      <c r="F15" s="3">
-        <v>1300</v>
-      </c>
       <c r="G15" s="3">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="H15" s="3">
+        <v>600</v>
+      </c>
+      <c r="I15" s="3">
         <v>200</v>
       </c>
-      <c r="I15" s="3">
-        <v>3000</v>
-      </c>
       <c r="J15" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K15" s="3">
         <v>3900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2300</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
       <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
         <v>100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-300</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>128100</v>
+        <v>540000</v>
       </c>
       <c r="E17" s="3">
-        <v>14200</v>
+        <v>120000</v>
       </c>
       <c r="F17" s="3">
-        <v>74300</v>
+        <v>13300</v>
       </c>
       <c r="G17" s="3">
-        <v>-67000</v>
+        <v>69600</v>
       </c>
       <c r="H17" s="3">
-        <v>83100</v>
+        <v>-62700</v>
       </c>
       <c r="I17" s="3">
-        <v>34700</v>
+        <v>77900</v>
       </c>
       <c r="J17" s="3">
+        <v>32600</v>
+      </c>
+      <c r="K17" s="3">
         <v>62900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>-20100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>-15000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23700</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-29000</v>
+        <v>-198300</v>
       </c>
       <c r="E18" s="3">
-        <v>62600</v>
+        <v>-27200</v>
       </c>
       <c r="F18" s="3">
-        <v>-23300</v>
+        <v>58700</v>
       </c>
       <c r="G18" s="3">
-        <v>105700</v>
+        <v>-21900</v>
       </c>
       <c r="H18" s="3">
-        <v>-52000</v>
+        <v>99000</v>
       </c>
       <c r="I18" s="3">
-        <v>30500</v>
+        <v>-48700</v>
       </c>
       <c r="J18" s="3">
+        <v>28600</v>
+      </c>
+      <c r="K18" s="3">
         <v>3300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>57100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>39700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>16700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>17400</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>33600</v>
+        <v>174100</v>
       </c>
       <c r="E20" s="3">
-        <v>47400</v>
+        <v>31500</v>
       </c>
       <c r="F20" s="3">
-        <v>34100</v>
+        <v>44400</v>
       </c>
       <c r="G20" s="3">
-        <v>12200</v>
+        <v>32000</v>
       </c>
       <c r="H20" s="3">
-        <v>-9400</v>
+        <v>11400</v>
       </c>
       <c r="I20" s="3">
-        <v>-19300</v>
+        <v>-8800</v>
       </c>
       <c r="J20" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="K20" s="3">
         <v>6500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-16500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3100</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6700</v>
+        <v>-17400</v>
       </c>
       <c r="E21" s="3">
-        <v>112200</v>
+        <v>6300</v>
       </c>
       <c r="F21" s="3">
-        <v>13300</v>
+        <v>105100</v>
       </c>
       <c r="G21" s="3">
-        <v>119200</v>
+        <v>12500</v>
       </c>
       <c r="H21" s="3">
-        <v>-60800</v>
+        <v>111700</v>
       </c>
       <c r="I21" s="3">
-        <v>18700</v>
+        <v>-57000</v>
       </c>
       <c r="J21" s="3">
+        <v>17500</v>
+      </c>
+      <c r="K21" s="3">
         <v>13600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>54000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>40600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>15300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>17600</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>13500</v>
+        <v>42000</v>
       </c>
       <c r="E22" s="3">
-        <v>19800</v>
+        <v>12600</v>
       </c>
       <c r="F22" s="3">
-        <v>38200</v>
+        <v>18600</v>
       </c>
       <c r="G22" s="3">
-        <v>25600</v>
+        <v>35800</v>
       </c>
       <c r="H22" s="3">
-        <v>7400</v>
+        <v>24000</v>
       </c>
       <c r="I22" s="3">
-        <v>15000</v>
+        <v>6900</v>
       </c>
       <c r="J22" s="3">
+        <v>14100</v>
+      </c>
+      <c r="K22" s="3">
         <v>14600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6400</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-66100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F23" s="3">
+        <v>84400</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="H23" s="3">
+        <v>86400</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-64500</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="L23" s="3">
+        <v>42900</v>
+      </c>
+      <c r="M23" s="3">
+        <v>31200</v>
+      </c>
+      <c r="N23" s="3">
         <v>-8900</v>
       </c>
-      <c r="E23" s="3">
-        <v>90100</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-27400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>92200</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-68800</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="K23" s="3">
-        <v>42900</v>
-      </c>
-      <c r="L23" s="3">
-        <v>31200</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7800</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-73300</v>
+        <v>-42200</v>
       </c>
       <c r="E24" s="3">
-        <v>6600</v>
+        <v>-68700</v>
       </c>
       <c r="F24" s="3">
-        <v>85000</v>
+        <v>6200</v>
       </c>
       <c r="G24" s="3">
-        <v>18300</v>
+        <v>79700</v>
       </c>
       <c r="H24" s="3">
-        <v>-7500</v>
+        <v>17200</v>
       </c>
       <c r="I24" s="3">
         <v>-7000</v>
       </c>
       <c r="J24" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="K24" s="3">
         <v>1700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>18100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2700</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>64500</v>
+        <v>-24000</v>
       </c>
       <c r="E26" s="3">
-        <v>83500</v>
+        <v>60400</v>
       </c>
       <c r="F26" s="3">
-        <v>-112500</v>
+        <v>78200</v>
       </c>
       <c r="G26" s="3">
-        <v>73900</v>
+        <v>-105400</v>
       </c>
       <c r="H26" s="3">
-        <v>-61300</v>
+        <v>69200</v>
       </c>
       <c r="I26" s="3">
-        <v>3200</v>
+        <v>-57500</v>
       </c>
       <c r="J26" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K26" s="3">
         <v>-6400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>24800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5200</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>63700</v>
+        <v>-19100</v>
       </c>
       <c r="E27" s="3">
-        <v>82700</v>
+        <v>59600</v>
       </c>
       <c r="F27" s="3">
-        <v>-82400</v>
+        <v>77500</v>
       </c>
       <c r="G27" s="3">
-        <v>48000</v>
+        <v>-77200</v>
       </c>
       <c r="H27" s="3">
-        <v>-58400</v>
+        <v>44900</v>
       </c>
       <c r="I27" s="3">
-        <v>-6300</v>
+        <v>-54700</v>
       </c>
       <c r="J27" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="K27" s="3">
         <v>-11100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>23300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>17900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1100</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,41 +1580,44 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-35000</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>-9000</v>
+        <v>-32800</v>
       </c>
       <c r="H29" s="3">
-        <v>-2600</v>
+        <v>-8400</v>
       </c>
       <c r="I29" s="3">
-        <v>22600</v>
+        <v>-2500</v>
       </c>
       <c r="J29" s="3">
+        <v>21200</v>
+      </c>
+      <c r="K29" s="3">
         <v>9800</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>2300</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>8</v>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-33600</v>
+        <v>-174100</v>
       </c>
       <c r="E32" s="3">
-        <v>-47400</v>
+        <v>-31500</v>
       </c>
       <c r="F32" s="3">
-        <v>-34100</v>
+        <v>-44400</v>
       </c>
       <c r="G32" s="3">
-        <v>-12200</v>
+        <v>-32000</v>
       </c>
       <c r="H32" s="3">
-        <v>9400</v>
+        <v>-11400</v>
       </c>
       <c r="I32" s="3">
-        <v>19300</v>
+        <v>8800</v>
       </c>
       <c r="J32" s="3">
+        <v>18100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-6500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>16500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3100</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>63700</v>
+        <v>-19100</v>
       </c>
       <c r="E33" s="3">
-        <v>82700</v>
+        <v>59600</v>
       </c>
       <c r="F33" s="3">
-        <v>-117400</v>
+        <v>77500</v>
       </c>
       <c r="G33" s="3">
-        <v>39000</v>
+        <v>-110000</v>
       </c>
       <c r="H33" s="3">
-        <v>-61000</v>
+        <v>36500</v>
       </c>
       <c r="I33" s="3">
-        <v>16300</v>
+        <v>-57200</v>
       </c>
       <c r="J33" s="3">
+        <v>15300</v>
+      </c>
+      <c r="K33" s="3">
         <v>-1200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>25700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1100</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>63700</v>
+        <v>-19100</v>
       </c>
       <c r="E35" s="3">
-        <v>82700</v>
+        <v>59600</v>
       </c>
       <c r="F35" s="3">
-        <v>-117400</v>
+        <v>77500</v>
       </c>
       <c r="G35" s="3">
-        <v>39000</v>
+        <v>-110000</v>
       </c>
       <c r="H35" s="3">
-        <v>-61000</v>
+        <v>36500</v>
       </c>
       <c r="I35" s="3">
-        <v>16300</v>
+        <v>-57200</v>
       </c>
       <c r="J35" s="3">
+        <v>15300</v>
+      </c>
+      <c r="K35" s="3">
         <v>-1200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>25700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1100</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44742</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44377</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44012</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43646</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43281</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42916</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42551</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42185</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41820</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41455</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41090</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,386 +1986,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>9700</v>
+        <v>29400</v>
       </c>
       <c r="E41" s="3">
-        <v>30600</v>
+        <v>9100</v>
       </c>
       <c r="F41" s="3">
-        <v>3500</v>
+        <v>28600</v>
       </c>
       <c r="G41" s="3">
-        <v>150600</v>
+        <v>3300</v>
       </c>
       <c r="H41" s="3">
-        <v>96000</v>
+        <v>141100</v>
       </c>
       <c r="I41" s="3">
-        <v>64400</v>
+        <v>89900</v>
       </c>
       <c r="J41" s="3">
+        <v>60400</v>
+      </c>
+      <c r="K41" s="3">
         <v>27600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>79300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5900</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>38200</v>
+        <v>125500</v>
       </c>
       <c r="E42" s="3">
-        <v>44100</v>
+        <v>35800</v>
       </c>
       <c r="F42" s="3">
-        <v>5800</v>
+        <v>41300</v>
       </c>
       <c r="G42" s="3">
-        <v>38000</v>
+        <v>5400</v>
       </c>
       <c r="H42" s="3">
-        <v>69600</v>
+        <v>35600</v>
       </c>
       <c r="I42" s="3">
-        <v>51700</v>
+        <v>65200</v>
       </c>
       <c r="J42" s="3">
+        <v>48500</v>
+      </c>
+      <c r="K42" s="3">
         <v>15900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>31200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2800</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>29500</v>
+        <v>80400</v>
       </c>
       <c r="E43" s="3">
-        <v>26000</v>
+        <v>27700</v>
       </c>
       <c r="F43" s="3">
-        <v>15700</v>
+        <v>24400</v>
       </c>
       <c r="G43" s="3">
-        <v>62400</v>
+        <v>14700</v>
       </c>
       <c r="H43" s="3">
-        <v>36400</v>
+        <v>58500</v>
       </c>
       <c r="I43" s="3">
-        <v>26500</v>
+        <v>34100</v>
       </c>
       <c r="J43" s="3">
+        <v>24800</v>
+      </c>
+      <c r="K43" s="3">
         <v>17700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>37400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9100</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>500</v>
+        <v>1100</v>
       </c>
       <c r="E44" s="3">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="F44" s="3">
         <v>300</v>
       </c>
       <c r="G44" s="3">
-        <v>11700</v>
+        <v>100</v>
       </c>
       <c r="H44" s="3">
-        <v>2400</v>
+        <v>7300</v>
       </c>
       <c r="I44" s="3">
-        <v>6700</v>
+        <v>1700</v>
       </c>
       <c r="J44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K44" s="3">
         <v>6100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9300</v>
-      </c>
-      <c r="L44" s="3">
-        <v>300</v>
       </c>
       <c r="M44" s="3">
         <v>300</v>
       </c>
       <c r="N44" s="3">
+        <v>300</v>
+      </c>
+      <c r="O44" s="3">
         <v>200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3000</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>400</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G45" s="3">
-        <v>80200</v>
+        <v>200</v>
       </c>
       <c r="H45" s="3">
-        <v>19800</v>
+        <v>78800</v>
       </c>
       <c r="I45" s="3">
-        <v>16400</v>
+        <v>19100</v>
       </c>
       <c r="J45" s="3">
+        <v>20700</v>
+      </c>
+      <c r="K45" s="3">
         <v>5500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>17800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1200</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>78000</v>
+        <v>236800</v>
       </c>
       <c r="E46" s="3">
-        <v>101500</v>
+        <v>73000</v>
       </c>
       <c r="F46" s="3">
-        <v>25300</v>
+        <v>95100</v>
       </c>
       <c r="G46" s="3">
-        <v>343000</v>
+        <v>23700</v>
       </c>
       <c r="H46" s="3">
-        <v>224100</v>
+        <v>321300</v>
       </c>
       <c r="I46" s="3">
-        <v>165900</v>
+        <v>210000</v>
       </c>
       <c r="J46" s="3">
+        <v>155400</v>
+      </c>
+      <c r="K46" s="3">
         <v>72700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>122300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>32200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>22100</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>48200</v>
+        <v>180700</v>
       </c>
       <c r="E47" s="3">
-        <v>51100</v>
+        <v>45200</v>
       </c>
       <c r="F47" s="3">
-        <v>29600</v>
+        <v>47900</v>
       </c>
       <c r="G47" s="3">
-        <v>168500</v>
+        <v>27700</v>
       </c>
       <c r="H47" s="3">
-        <v>73800</v>
+        <v>157900</v>
       </c>
       <c r="I47" s="3">
-        <v>62500</v>
+        <v>69100</v>
       </c>
       <c r="J47" s="3">
+        <v>58600</v>
+      </c>
+      <c r="K47" s="3">
         <v>14500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>61100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>32800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>31200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>27000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>54000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>647200</v>
+        <v>1820000</v>
       </c>
       <c r="E48" s="3">
-        <v>723900</v>
+        <v>606400</v>
       </c>
       <c r="F48" s="3">
-        <v>342400</v>
+        <v>678300</v>
       </c>
       <c r="G48" s="3">
-        <v>475400</v>
+        <v>320800</v>
       </c>
       <c r="H48" s="3">
-        <v>405600</v>
+        <v>445400</v>
       </c>
       <c r="I48" s="3">
-        <v>375800</v>
+        <v>380000</v>
       </c>
       <c r="J48" s="3">
+        <v>352100</v>
+      </c>
+      <c r="K48" s="3">
         <v>141000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>447900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>171600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>193500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>111100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>76200</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>8800</v>
+        <v>67200</v>
       </c>
       <c r="E49" s="3">
-        <v>8100</v>
+        <v>8300</v>
       </c>
       <c r="F49" s="3">
-        <v>4400</v>
+        <v>7600</v>
       </c>
       <c r="G49" s="3">
-        <v>46300</v>
+        <v>4100</v>
       </c>
       <c r="H49" s="3">
-        <v>28400</v>
+        <v>43400</v>
       </c>
       <c r="I49" s="3">
-        <v>21400</v>
+        <v>26600</v>
       </c>
       <c r="J49" s="3">
+        <v>20100</v>
+      </c>
+      <c r="K49" s="3">
         <v>13700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>33600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2300</v>
       </c>
-      <c r="O49" s="3" t="s">
+      <c r="P49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7700</v>
+        <v>26700</v>
       </c>
       <c r="E52" s="3">
-        <v>7500</v>
+        <v>7200</v>
       </c>
       <c r="F52" s="3">
-        <v>3800</v>
+        <v>7000</v>
       </c>
       <c r="G52" s="3">
-        <v>12500</v>
+        <v>3600</v>
       </c>
       <c r="H52" s="3">
-        <v>21000</v>
+        <v>11700</v>
       </c>
       <c r="I52" s="3">
-        <v>38800</v>
+        <v>19700</v>
       </c>
       <c r="J52" s="3">
+        <v>36400</v>
+      </c>
+      <c r="K52" s="3">
         <v>14600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>27200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6200</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>789900</v>
+        <v>2331400</v>
       </c>
       <c r="E54" s="3">
-        <v>892100</v>
+        <v>740100</v>
       </c>
       <c r="F54" s="3">
-        <v>405500</v>
+        <v>835800</v>
       </c>
       <c r="G54" s="3">
-        <v>1045700</v>
+        <v>379900</v>
       </c>
       <c r="H54" s="3">
-        <v>753000</v>
+        <v>979700</v>
       </c>
       <c r="I54" s="3">
-        <v>584800</v>
+        <v>705500</v>
       </c>
       <c r="J54" s="3">
+        <v>547900</v>
+      </c>
+      <c r="K54" s="3">
         <v>256700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>549500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>192200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>224400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>113000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>151400</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>33400</v>
+        <v>75600</v>
       </c>
       <c r="E57" s="3">
-        <v>20400</v>
+        <v>31300</v>
       </c>
       <c r="F57" s="3">
-        <v>9300</v>
+        <v>19100</v>
       </c>
       <c r="G57" s="3">
-        <v>49500</v>
+        <v>8700</v>
       </c>
       <c r="H57" s="3">
-        <v>29400</v>
+        <v>46300</v>
       </c>
       <c r="I57" s="3">
-        <v>25400</v>
+        <v>27600</v>
       </c>
       <c r="J57" s="3">
+        <v>23800</v>
+      </c>
+      <c r="K57" s="3">
         <v>14100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>31700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1800</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>45500</v>
+        <v>190600</v>
       </c>
       <c r="E58" s="3">
-        <v>147800</v>
+        <v>42600</v>
       </c>
       <c r="F58" s="3">
-        <v>28100</v>
+        <v>138500</v>
       </c>
       <c r="G58" s="3">
-        <v>138700</v>
+        <v>26400</v>
       </c>
       <c r="H58" s="3">
-        <v>122700</v>
+        <v>130000</v>
       </c>
       <c r="I58" s="3">
-        <v>44200</v>
+        <v>115000</v>
       </c>
       <c r="J58" s="3">
+        <v>41400</v>
+      </c>
+      <c r="K58" s="3">
         <v>22100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>63600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>18300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>14700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13200</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5200</v>
+        <v>19700</v>
       </c>
       <c r="E59" s="3">
-        <v>38600</v>
+        <v>4900</v>
       </c>
       <c r="F59" s="3">
-        <v>2900</v>
+        <v>36200</v>
       </c>
       <c r="G59" s="3">
-        <v>50900</v>
+        <v>2700</v>
       </c>
       <c r="H59" s="3">
-        <v>15700</v>
+        <v>47600</v>
       </c>
       <c r="I59" s="3">
-        <v>11300</v>
+        <v>14700</v>
       </c>
       <c r="J59" s="3">
+        <v>10600</v>
+      </c>
+      <c r="K59" s="3">
         <v>15300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>29400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14300</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>84100</v>
+        <v>285900</v>
       </c>
       <c r="E60" s="3">
-        <v>206800</v>
+        <v>78800</v>
       </c>
       <c r="F60" s="3">
-        <v>40300</v>
+        <v>193800</v>
       </c>
       <c r="G60" s="3">
-        <v>239100</v>
+        <v>37800</v>
       </c>
       <c r="H60" s="3">
-        <v>117300</v>
+        <v>224000</v>
       </c>
       <c r="I60" s="3">
-        <v>81000</v>
+        <v>109900</v>
       </c>
       <c r="J60" s="3">
+        <v>75800</v>
+      </c>
+      <c r="K60" s="3">
         <v>51500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>124700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>19600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>25300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>29400</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>77700</v>
+        <v>202200</v>
       </c>
       <c r="E61" s="3">
-        <v>34000</v>
+        <v>72800</v>
       </c>
       <c r="F61" s="3">
-        <v>86600</v>
+        <v>31800</v>
       </c>
       <c r="G61" s="3">
-        <v>518800</v>
+        <v>81100</v>
       </c>
       <c r="H61" s="3">
-        <v>423600</v>
+        <v>486100</v>
       </c>
       <c r="I61" s="3">
-        <v>312600</v>
+        <v>396900</v>
       </c>
       <c r="J61" s="3">
+        <v>292900</v>
+      </c>
+      <c r="K61" s="3">
         <v>121500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>259300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>37300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>39700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>47400</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>201500</v>
+        <v>644800</v>
       </c>
       <c r="E62" s="3">
-        <v>245100</v>
+        <v>188800</v>
       </c>
       <c r="F62" s="3">
-        <v>128000</v>
+        <v>229700</v>
       </c>
       <c r="G62" s="3">
-        <v>83300</v>
+        <v>120000</v>
       </c>
       <c r="H62" s="3">
-        <v>75900</v>
+        <v>78100</v>
       </c>
       <c r="I62" s="3">
-        <v>58600</v>
+        <v>71100</v>
       </c>
       <c r="J62" s="3">
+        <v>54900</v>
+      </c>
+      <c r="K62" s="3">
         <v>31100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>64400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>48300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>52600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12800</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>388000</v>
+        <v>1209600</v>
       </c>
       <c r="E66" s="3">
-        <v>511900</v>
+        <v>363500</v>
       </c>
       <c r="F66" s="3">
-        <v>293000</v>
+        <v>479700</v>
       </c>
       <c r="G66" s="3">
-        <v>950400</v>
+        <v>274500</v>
       </c>
       <c r="H66" s="3">
-        <v>702100</v>
+        <v>890500</v>
       </c>
       <c r="I66" s="3">
-        <v>516700</v>
+        <v>657800</v>
       </c>
       <c r="J66" s="3">
+        <v>484100</v>
+      </c>
+      <c r="K66" s="3">
         <v>228000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>487700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>100200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>123100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>75700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>97800</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>159500</v>
+        <v>318900</v>
       </c>
       <c r="E72" s="3">
-        <v>137800</v>
+        <v>149500</v>
       </c>
       <c r="F72" s="3">
-        <v>29700</v>
+        <v>129100</v>
       </c>
       <c r="G72" s="3">
-        <v>47300</v>
+        <v>27800</v>
       </c>
       <c r="H72" s="3">
-        <v>19000</v>
+        <v>44300</v>
       </c>
       <c r="I72" s="3">
-        <v>45800</v>
+        <v>17800</v>
       </c>
       <c r="J72" s="3">
+        <v>42900</v>
+      </c>
+      <c r="K72" s="3">
         <v>27000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>57500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>83700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>95100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>401900</v>
+        <v>1121800</v>
       </c>
       <c r="E76" s="3">
-        <v>380100</v>
+        <v>376500</v>
       </c>
       <c r="F76" s="3">
-        <v>112500</v>
+        <v>356200</v>
       </c>
       <c r="G76" s="3">
-        <v>95200</v>
+        <v>105400</v>
       </c>
       <c r="H76" s="3">
-        <v>50900</v>
+        <v>89200</v>
       </c>
       <c r="I76" s="3">
-        <v>68100</v>
+        <v>47700</v>
       </c>
       <c r="J76" s="3">
+        <v>63800</v>
+      </c>
+      <c r="K76" s="3">
         <v>28700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>61900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>91900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>101400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>37300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>53600</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44742</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44377</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44012</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43646</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43281</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42916</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42551</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42185</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41820</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41455</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41090</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>63700</v>
+        <v>-19100</v>
       </c>
       <c r="E81" s="3">
-        <v>82700</v>
+        <v>59600</v>
       </c>
       <c r="F81" s="3">
-        <v>-117400</v>
+        <v>77500</v>
       </c>
       <c r="G81" s="3">
-        <v>39000</v>
+        <v>-110000</v>
       </c>
       <c r="H81" s="3">
-        <v>-61000</v>
+        <v>36500</v>
       </c>
       <c r="I81" s="3">
-        <v>16300</v>
+        <v>-57200</v>
       </c>
       <c r="J81" s="3">
+        <v>15300</v>
+      </c>
+      <c r="K81" s="3">
         <v>-1200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>25700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1100</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F83" s="3">
         <v>2100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I83" s="3">
+        <v>600</v>
+      </c>
+      <c r="J83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="L83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="M83" s="3">
+        <v>200</v>
+      </c>
+      <c r="N83" s="3">
         <v>2200</v>
       </c>
-      <c r="F83" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H83" s="3">
-        <v>600</v>
-      </c>
-      <c r="I83" s="3">
-        <v>7500</v>
-      </c>
-      <c r="J83" s="3">
-        <v>3700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>4400</v>
-      </c>
-      <c r="L83" s="3">
-        <v>200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>2200</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3400</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>39200</v>
+        <v>96300</v>
       </c>
       <c r="E89" s="3">
-        <v>29400</v>
+        <v>36700</v>
       </c>
       <c r="F89" s="3">
-        <v>-565400</v>
+        <v>27500</v>
       </c>
       <c r="G89" s="3">
-        <v>85100</v>
+        <v>-529800</v>
       </c>
       <c r="H89" s="3">
-        <v>45100</v>
+        <v>79700</v>
       </c>
       <c r="I89" s="3">
+        <v>42200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>14900</v>
+      </c>
+      <c r="K89" s="3">
+        <v>10100</v>
+      </c>
+      <c r="L89" s="3">
+        <v>11800</v>
+      </c>
+      <c r="M89" s="3">
+        <v>6100</v>
+      </c>
+      <c r="N89" s="3">
+        <v>10100</v>
+      </c>
+      <c r="O89" s="3">
+        <v>11700</v>
+      </c>
+      <c r="P89" s="3">
         <v>15900</v>
       </c>
-      <c r="J89" s="3">
-        <v>10100</v>
-      </c>
-      <c r="K89" s="3">
-        <v>11800</v>
-      </c>
-      <c r="L89" s="3">
-        <v>6100</v>
-      </c>
-      <c r="M89" s="3">
-        <v>10100</v>
-      </c>
-      <c r="N89" s="3">
-        <v>11700</v>
-      </c>
-      <c r="O89" s="3">
-        <v>15900</v>
-      </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-7400</v>
+        <v>-16900</v>
       </c>
       <c r="E91" s="3">
-        <v>-15500</v>
+        <v>-7000</v>
       </c>
       <c r="F91" s="3">
-        <v>-5100</v>
+        <v>-14500</v>
       </c>
       <c r="G91" s="3">
-        <v>-10700</v>
+        <v>-4800</v>
       </c>
       <c r="H91" s="3">
-        <v>-7400</v>
+        <v>-10100</v>
       </c>
       <c r="I91" s="3">
-        <v>-10300</v>
+        <v>-6900</v>
       </c>
       <c r="J91" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="K91" s="3">
         <v>-4500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3800</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>29400</v>
+        <v>86600</v>
       </c>
       <c r="E94" s="3">
-        <v>26800</v>
+        <v>27500</v>
       </c>
       <c r="F94" s="3">
-        <v>264300</v>
+        <v>25100</v>
       </c>
       <c r="G94" s="3">
-        <v>124700</v>
+        <v>247600</v>
       </c>
       <c r="H94" s="3">
-        <v>18700</v>
+        <v>116800</v>
       </c>
       <c r="I94" s="3">
-        <v>-23700</v>
+        <v>17500</v>
       </c>
       <c r="J94" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>23500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5700</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-35800</v>
+        <v>-158500</v>
       </c>
       <c r="E96" s="3">
+        <v>-33600</v>
+      </c>
+      <c r="F96" s="3">
         <v>-400</v>
       </c>
-      <c r="F96" s="3">
-        <v>-10200</v>
-      </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-9500</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-2900</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-2700</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-6000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-90000</v>
+        <v>-198600</v>
       </c>
       <c r="E100" s="3">
-        <v>-32700</v>
+        <v>-84400</v>
       </c>
       <c r="F100" s="3">
-        <v>-189600</v>
+        <v>-30600</v>
       </c>
       <c r="G100" s="3">
-        <v>-221700</v>
+        <v>-177600</v>
       </c>
       <c r="H100" s="3">
-        <v>-46300</v>
+        <v>-207700</v>
       </c>
       <c r="I100" s="3">
-        <v>-4800</v>
+        <v>-43400</v>
       </c>
       <c r="J100" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K100" s="3">
         <v>1700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-11300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-10100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-11300</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
-        <v>-34200</v>
-      </c>
       <c r="G101" s="3">
-        <v>23900</v>
+        <v>-32100</v>
       </c>
       <c r="H101" s="3">
-        <v>-11300</v>
+        <v>22400</v>
       </c>
       <c r="I101" s="3">
-        <v>22200</v>
+        <v>-10600</v>
       </c>
       <c r="J101" s="3">
+        <v>20800</v>
+      </c>
+      <c r="K101" s="3">
         <v>2900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>14600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-20900</v>
+        <v>-4300</v>
       </c>
       <c r="E102" s="3">
-        <v>23000</v>
+        <v>-19600</v>
       </c>
       <c r="F102" s="3">
-        <v>-525000</v>
+        <v>21500</v>
       </c>
       <c r="G102" s="3">
-        <v>11900</v>
+        <v>-491900</v>
       </c>
       <c r="H102" s="3">
-        <v>6200</v>
+        <v>11200</v>
       </c>
       <c r="I102" s="3">
-        <v>9500</v>
+        <v>5800</v>
       </c>
       <c r="J102" s="3">
+        <v>8900</v>
+      </c>
+      <c r="K102" s="3">
         <v>12400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>38600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/IRS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IRS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>IRS</t>
   </si>
@@ -662,7 +662,11 @@
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -726,25 +730,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>341700</v>
+        <v>397600</v>
       </c>
       <c r="E8" s="3">
-        <v>92900</v>
+        <v>1330400</v>
       </c>
       <c r="F8" s="3">
-        <v>71900</v>
+        <v>2029600</v>
       </c>
       <c r="G8" s="3">
-        <v>47700</v>
+        <v>317500</v>
       </c>
       <c r="H8" s="3">
-        <v>36300</v>
+        <v>747400</v>
       </c>
       <c r="I8" s="3">
-        <v>29100</v>
+        <v>411600</v>
       </c>
       <c r="J8" s="3">
-        <v>61200</v>
+        <v>2569700</v>
       </c>
       <c r="K8" s="3">
         <v>66200</v>
@@ -771,25 +775,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>113600</v>
+        <v>113000</v>
       </c>
       <c r="E9" s="3">
-        <v>32000</v>
+        <v>416900</v>
       </c>
       <c r="F9" s="3">
-        <v>27200</v>
+        <v>705000</v>
       </c>
       <c r="G9" s="3">
-        <v>24800</v>
+        <v>242400</v>
       </c>
       <c r="H9" s="3">
-        <v>15600</v>
+        <v>206500</v>
       </c>
       <c r="I9" s="3">
-        <v>10900</v>
+        <v>247200</v>
       </c>
       <c r="J9" s="3">
-        <v>36000</v>
+        <v>1671000</v>
       </c>
       <c r="K9" s="3">
         <v>92200</v>
@@ -816,25 +820,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>228100</v>
+        <v>284600</v>
       </c>
       <c r="E10" s="3">
-        <v>60800</v>
+        <v>913500</v>
       </c>
       <c r="F10" s="3">
-        <v>44700</v>
+        <v>1324600</v>
       </c>
       <c r="G10" s="3">
-        <v>22900</v>
+        <v>75100</v>
       </c>
       <c r="H10" s="3">
-        <v>20600</v>
+        <v>540900</v>
       </c>
       <c r="I10" s="3">
-        <v>18200</v>
+        <v>164400</v>
       </c>
       <c r="J10" s="3">
-        <v>25100</v>
+        <v>898700</v>
       </c>
       <c r="K10" s="3">
         <v>-26000</v>
@@ -970,25 +974,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>8400</v>
+        <v>393500</v>
       </c>
       <c r="E14" s="3">
-        <v>7800</v>
+        <v>826300</v>
       </c>
       <c r="F14" s="3">
-        <v>600</v>
+        <v>-948800</v>
       </c>
       <c r="G14" s="3">
-        <v>200</v>
+        <v>345700</v>
       </c>
       <c r="H14" s="3">
-        <v>2800</v>
+        <v>-1178000</v>
       </c>
       <c r="I14" s="3">
-        <v>400</v>
+        <v>1409000</v>
       </c>
       <c r="J14" s="3">
-        <v>-1400</v>
+        <v>-515800</v>
       </c>
       <c r="K14" s="3">
         <v>500</v>
@@ -1015,25 +1019,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1800</v>
+        <v>4900</v>
       </c>
       <c r="E15" s="3">
-        <v>600</v>
+        <v>19100</v>
       </c>
       <c r="F15" s="3">
-        <v>700</v>
+        <v>59500</v>
       </c>
       <c r="G15" s="3">
-        <v>1200</v>
+        <v>23700</v>
       </c>
       <c r="H15" s="3">
-        <v>600</v>
+        <v>16700</v>
       </c>
       <c r="I15" s="3">
-        <v>200</v>
+        <v>13200</v>
       </c>
       <c r="J15" s="3">
-        <v>2800</v>
+        <v>193700</v>
       </c>
       <c r="K15" s="3">
         <v>3900</v>
@@ -1076,25 +1080,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>540000</v>
+        <v>178200</v>
       </c>
       <c r="E17" s="3">
-        <v>120000</v>
+        <v>851200</v>
       </c>
       <c r="F17" s="3">
-        <v>13300</v>
+        <v>1242200</v>
       </c>
       <c r="G17" s="3">
-        <v>69600</v>
+        <v>413700</v>
       </c>
       <c r="H17" s="3">
-        <v>-62700</v>
+        <v>324900</v>
       </c>
       <c r="I17" s="3">
-        <v>77900</v>
+        <v>393100</v>
       </c>
       <c r="J17" s="3">
-        <v>32600</v>
+        <v>2435600</v>
       </c>
       <c r="K17" s="3">
         <v>62900</v>
@@ -1121,25 +1125,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-198300</v>
+        <v>219400</v>
       </c>
       <c r="E18" s="3">
-        <v>-27200</v>
+        <v>479200</v>
       </c>
       <c r="F18" s="3">
-        <v>58700</v>
+        <v>787400</v>
       </c>
       <c r="G18" s="3">
-        <v>-21900</v>
+        <v>-96200</v>
       </c>
       <c r="H18" s="3">
-        <v>99000</v>
+        <v>422500</v>
       </c>
       <c r="I18" s="3">
-        <v>-48700</v>
+        <v>18500</v>
       </c>
       <c r="J18" s="3">
-        <v>28600</v>
+        <v>134100</v>
       </c>
       <c r="K18" s="3">
         <v>3300</v>
@@ -1185,25 +1189,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>174100</v>
+        <v>-109300</v>
       </c>
       <c r="E20" s="3">
-        <v>31500</v>
+        <v>-385700</v>
       </c>
       <c r="F20" s="3">
-        <v>44400</v>
+        <v>-1165400</v>
       </c>
       <c r="G20" s="3">
-        <v>32000</v>
+        <v>-424300</v>
       </c>
       <c r="H20" s="3">
-        <v>11400</v>
+        <v>232500</v>
       </c>
       <c r="I20" s="3">
-        <v>-8800</v>
+        <v>-67300</v>
       </c>
       <c r="J20" s="3">
-        <v>-18100</v>
+        <v>578000</v>
       </c>
       <c r="K20" s="3">
         <v>6500</v>
@@ -1230,25 +1234,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-17400</v>
+        <v>333700</v>
       </c>
       <c r="E21" s="3">
-        <v>6300</v>
+        <v>883900</v>
       </c>
       <c r="F21" s="3">
-        <v>105100</v>
+        <v>2012300</v>
       </c>
       <c r="G21" s="3">
-        <v>12500</v>
+        <v>351800</v>
       </c>
       <c r="H21" s="3">
-        <v>111700</v>
+        <v>206600</v>
       </c>
       <c r="I21" s="3">
-        <v>-57000</v>
+        <v>99000</v>
       </c>
       <c r="J21" s="3">
-        <v>17500</v>
+        <v>-250200</v>
       </c>
       <c r="K21" s="3">
         <v>13600</v>
@@ -1275,25 +1279,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>42000</v>
+        <v>44300</v>
       </c>
       <c r="E22" s="3">
-        <v>12600</v>
+        <v>175600</v>
       </c>
       <c r="F22" s="3">
-        <v>18600</v>
+        <v>530300</v>
       </c>
       <c r="G22" s="3">
-        <v>35800</v>
+        <v>257600</v>
       </c>
       <c r="H22" s="3">
-        <v>24000</v>
+        <v>202200</v>
       </c>
       <c r="I22" s="3">
-        <v>6900</v>
+        <v>157500</v>
       </c>
       <c r="J22" s="3">
-        <v>14100</v>
+        <v>626600</v>
       </c>
       <c r="K22" s="3">
         <v>14600</v>
@@ -1320,25 +1324,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-66100</v>
+        <v>-69700</v>
       </c>
       <c r="E23" s="3">
-        <v>-8300</v>
+        <v>-115500</v>
       </c>
       <c r="F23" s="3">
-        <v>84400</v>
+        <v>2409100</v>
       </c>
       <c r="G23" s="3">
-        <v>-25700</v>
+        <v>-258300</v>
       </c>
       <c r="H23" s="3">
-        <v>86400</v>
+        <v>1179200</v>
       </c>
       <c r="I23" s="3">
-        <v>-64500</v>
+        <v>-1465400</v>
       </c>
       <c r="J23" s="3">
-        <v>-3600</v>
+        <v>-495700</v>
       </c>
       <c r="K23" s="3">
         <v>-4800</v>
@@ -1365,25 +1369,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-42200</v>
+        <v>-44500</v>
       </c>
       <c r="E24" s="3">
-        <v>-68700</v>
+        <v>-956500</v>
       </c>
       <c r="F24" s="3">
-        <v>6200</v>
+        <v>177200</v>
       </c>
       <c r="G24" s="3">
-        <v>79700</v>
+        <v>800400</v>
       </c>
       <c r="H24" s="3">
-        <v>17200</v>
+        <v>234300</v>
       </c>
       <c r="I24" s="3">
-        <v>-7000</v>
+        <v>-159700</v>
       </c>
       <c r="J24" s="3">
-        <v>-6500</v>
+        <v>-384300</v>
       </c>
       <c r="K24" s="3">
         <v>1700</v>
@@ -1455,25 +1459,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-24000</v>
+        <v>-25300</v>
       </c>
       <c r="E26" s="3">
-        <v>60400</v>
+        <v>840900</v>
       </c>
       <c r="F26" s="3">
-        <v>78200</v>
+        <v>2231900</v>
       </c>
       <c r="G26" s="3">
-        <v>-105400</v>
+        <v>-1058700</v>
       </c>
       <c r="H26" s="3">
-        <v>69200</v>
+        <v>944900</v>
       </c>
       <c r="I26" s="3">
-        <v>-57500</v>
+        <v>-1305600</v>
       </c>
       <c r="J26" s="3">
-        <v>3000</v>
+        <v>-111500</v>
       </c>
       <c r="K26" s="3">
         <v>-6400</v>
@@ -1500,25 +1504,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-19100</v>
+        <v>-20100</v>
       </c>
       <c r="E27" s="3">
-        <v>59600</v>
+        <v>830200</v>
       </c>
       <c r="F27" s="3">
-        <v>77500</v>
+        <v>2210100</v>
       </c>
       <c r="G27" s="3">
-        <v>-77200</v>
+        <v>-1105300</v>
       </c>
       <c r="H27" s="3">
-        <v>44900</v>
+        <v>498200</v>
       </c>
       <c r="I27" s="3">
-        <v>-54700</v>
+        <v>-1299300</v>
       </c>
       <c r="J27" s="3">
-        <v>-5900</v>
+        <v>726300</v>
       </c>
       <c r="K27" s="3">
         <v>-11100</v>
@@ -1589,8 +1593,8 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -1599,16 +1603,16 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>-32800</v>
+        <v>-329500</v>
       </c>
       <c r="H29" s="3">
-        <v>-8400</v>
+        <v>-115100</v>
       </c>
       <c r="I29" s="3">
-        <v>-2500</v>
+        <v>-56200</v>
       </c>
       <c r="J29" s="3">
-        <v>21200</v>
+        <v>1257500</v>
       </c>
       <c r="K29" s="3">
         <v>9800</v>
@@ -1725,25 +1729,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-174100</v>
+        <v>109300</v>
       </c>
       <c r="E32" s="3">
-        <v>-31500</v>
+        <v>385700</v>
       </c>
       <c r="F32" s="3">
-        <v>-44400</v>
+        <v>1165400</v>
       </c>
       <c r="G32" s="3">
-        <v>-32000</v>
+        <v>424300</v>
       </c>
       <c r="H32" s="3">
-        <v>-11400</v>
+        <v>-232500</v>
       </c>
       <c r="I32" s="3">
-        <v>8800</v>
+        <v>67300</v>
       </c>
       <c r="J32" s="3">
-        <v>18100</v>
+        <v>-578000</v>
       </c>
       <c r="K32" s="3">
         <v>-6500</v>
@@ -1770,25 +1774,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-19100</v>
+        <v>-20200</v>
       </c>
       <c r="E33" s="3">
-        <v>59600</v>
+        <v>830200</v>
       </c>
       <c r="F33" s="3">
-        <v>77500</v>
+        <v>2210100</v>
       </c>
       <c r="G33" s="3">
-        <v>-110000</v>
+        <v>-1105300</v>
       </c>
       <c r="H33" s="3">
-        <v>36500</v>
+        <v>498200</v>
       </c>
       <c r="I33" s="3">
-        <v>-57200</v>
+        <v>-1299300</v>
       </c>
       <c r="J33" s="3">
-        <v>15300</v>
+        <v>726300</v>
       </c>
       <c r="K33" s="3">
         <v>-1200</v>
@@ -1860,25 +1864,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-19100</v>
+        <v>-20200</v>
       </c>
       <c r="E35" s="3">
-        <v>59600</v>
+        <v>830200</v>
       </c>
       <c r="F35" s="3">
-        <v>77500</v>
+        <v>2210100</v>
       </c>
       <c r="G35" s="3">
-        <v>-110000</v>
+        <v>-1105300</v>
       </c>
       <c r="H35" s="3">
-        <v>36500</v>
+        <v>498200</v>
       </c>
       <c r="I35" s="3">
-        <v>-57200</v>
+        <v>-1299300</v>
       </c>
       <c r="J35" s="3">
-        <v>15300</v>
+        <v>726300</v>
       </c>
       <c r="K35" s="3">
         <v>-1200</v>
@@ -1993,25 +1997,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>29400</v>
+        <v>31000</v>
       </c>
       <c r="E41" s="3">
-        <v>9100</v>
+        <v>126400</v>
       </c>
       <c r="F41" s="3">
-        <v>28600</v>
+        <v>220000</v>
       </c>
       <c r="G41" s="3">
-        <v>3300</v>
+        <v>33100</v>
       </c>
       <c r="H41" s="3">
-        <v>141100</v>
+        <v>1926300</v>
       </c>
       <c r="I41" s="3">
-        <v>89900</v>
+        <v>2042600</v>
       </c>
       <c r="J41" s="3">
-        <v>60400</v>
+        <v>2003400</v>
       </c>
       <c r="K41" s="3">
         <v>27600</v>
@@ -2038,25 +2042,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>125500</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>35800</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>41300</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>35600</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>65200</v>
+        <v>393800</v>
       </c>
       <c r="J42" s="3">
-        <v>48500</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>15900</v>
@@ -2083,25 +2087,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>80400</v>
+        <v>84700</v>
       </c>
       <c r="E43" s="3">
-        <v>27700</v>
+        <v>385100</v>
       </c>
       <c r="F43" s="3">
-        <v>24400</v>
+        <v>187400</v>
       </c>
       <c r="G43" s="3">
-        <v>14700</v>
+        <v>148000</v>
       </c>
       <c r="H43" s="3">
-        <v>58500</v>
+        <v>798400</v>
       </c>
       <c r="I43" s="3">
-        <v>34100</v>
+        <v>774500</v>
       </c>
       <c r="J43" s="3">
-        <v>24800</v>
+        <v>824000</v>
       </c>
       <c r="K43" s="3">
         <v>17700</v>
@@ -2128,25 +2132,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="E44" s="3">
-        <v>300</v>
+        <v>6900</v>
       </c>
       <c r="F44" s="3">
-        <v>300</v>
+        <v>5500</v>
       </c>
       <c r="G44" s="3">
-        <v>100</v>
+        <v>3200</v>
       </c>
       <c r="H44" s="3">
-        <v>7300</v>
+        <v>149200</v>
       </c>
       <c r="I44" s="3">
-        <v>1700</v>
+        <v>51100</v>
       </c>
       <c r="J44" s="3">
-        <v>1000</v>
+        <v>209700</v>
       </c>
       <c r="K44" s="3">
         <v>6100</v>
@@ -2172,26 +2176,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>200</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H45" s="3">
-        <v>78800</v>
+        <v>1025400</v>
       </c>
       <c r="I45" s="3">
-        <v>19100</v>
+        <v>421000</v>
       </c>
       <c r="J45" s="3">
-        <v>20700</v>
+        <v>511300</v>
       </c>
       <c r="K45" s="3">
         <v>5500</v>
@@ -2218,25 +2222,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>236800</v>
+        <v>117400</v>
       </c>
       <c r="E46" s="3">
-        <v>73000</v>
+        <v>518400</v>
       </c>
       <c r="F46" s="3">
-        <v>95100</v>
+        <v>412800</v>
       </c>
       <c r="G46" s="3">
-        <v>23700</v>
+        <v>184300</v>
       </c>
       <c r="H46" s="3">
-        <v>321300</v>
+        <v>3899300</v>
       </c>
       <c r="I46" s="3">
-        <v>210000</v>
+        <v>3683100</v>
       </c>
       <c r="J46" s="3">
-        <v>155400</v>
+        <v>3548500</v>
       </c>
       <c r="K46" s="3">
         <v>72700</v>
@@ -2263,25 +2267,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>180700</v>
+        <v>285300</v>
       </c>
       <c r="E47" s="3">
-        <v>45200</v>
+        <v>1062600</v>
       </c>
       <c r="F47" s="3">
-        <v>47900</v>
+        <v>610000</v>
       </c>
       <c r="G47" s="3">
-        <v>27700</v>
+        <v>283500</v>
       </c>
       <c r="H47" s="3">
-        <v>157900</v>
+        <v>2147200</v>
       </c>
       <c r="I47" s="3">
-        <v>69100</v>
+        <v>2376800</v>
       </c>
       <c r="J47" s="3">
-        <v>58600</v>
+        <v>3509900</v>
       </c>
       <c r="K47" s="3">
         <v>14500</v>
@@ -2308,25 +2312,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1820000</v>
+        <v>51800</v>
       </c>
       <c r="E48" s="3">
-        <v>606400</v>
+        <v>189400</v>
       </c>
       <c r="F48" s="3">
-        <v>678300</v>
+        <v>158900</v>
       </c>
       <c r="G48" s="3">
-        <v>320800</v>
+        <v>84900</v>
       </c>
       <c r="H48" s="3">
-        <v>445400</v>
+        <v>1227700</v>
       </c>
       <c r="I48" s="3">
-        <v>380000</v>
+        <v>753900</v>
       </c>
       <c r="J48" s="3">
-        <v>352100</v>
+        <v>762800</v>
       </c>
       <c r="K48" s="3">
         <v>141000</v>
@@ -2353,25 +2357,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>67200</v>
+        <v>70800</v>
       </c>
       <c r="E49" s="3">
-        <v>8300</v>
+        <v>115000</v>
       </c>
       <c r="F49" s="3">
-        <v>7600</v>
+        <v>58200</v>
       </c>
       <c r="G49" s="3">
-        <v>4100</v>
+        <v>41100</v>
       </c>
       <c r="H49" s="3">
-        <v>43400</v>
+        <v>592300</v>
       </c>
       <c r="I49" s="3">
-        <v>26600</v>
+        <v>605000</v>
       </c>
       <c r="J49" s="3">
-        <v>20100</v>
+        <v>665600</v>
       </c>
       <c r="K49" s="3">
         <v>13700</v>
@@ -2488,25 +2492,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>26700</v>
+        <v>1926100</v>
       </c>
       <c r="E52" s="3">
-        <v>7200</v>
+        <v>8402900</v>
       </c>
       <c r="F52" s="3">
-        <v>7000</v>
+        <v>5177000</v>
       </c>
       <c r="G52" s="3">
-        <v>3600</v>
+        <v>3215000</v>
       </c>
       <c r="H52" s="3">
-        <v>11700</v>
+        <v>5491000</v>
       </c>
       <c r="I52" s="3">
-        <v>19700</v>
+        <v>8597100</v>
       </c>
       <c r="J52" s="3">
-        <v>36400</v>
+        <v>9675200</v>
       </c>
       <c r="K52" s="3">
         <v>14600</v>
@@ -2578,25 +2582,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2331400</v>
+        <v>2458100</v>
       </c>
       <c r="E54" s="3">
-        <v>740100</v>
+        <v>10300800</v>
       </c>
       <c r="F54" s="3">
-        <v>835800</v>
+        <v>6418200</v>
       </c>
       <c r="G54" s="3">
-        <v>379900</v>
+        <v>3816400</v>
       </c>
       <c r="H54" s="3">
-        <v>979700</v>
+        <v>13371000</v>
       </c>
       <c r="I54" s="3">
-        <v>705500</v>
+        <v>16029300</v>
       </c>
       <c r="J54" s="3">
-        <v>547900</v>
+        <v>18181200</v>
       </c>
       <c r="K54" s="3">
         <v>256700</v>
@@ -2661,25 +2665,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>75600</v>
+        <v>79700</v>
       </c>
       <c r="E57" s="3">
-        <v>31300</v>
+        <v>435100</v>
       </c>
       <c r="F57" s="3">
-        <v>19100</v>
+        <v>146800</v>
       </c>
       <c r="G57" s="3">
-        <v>8700</v>
+        <v>87400</v>
       </c>
       <c r="H57" s="3">
-        <v>46300</v>
+        <v>632600</v>
       </c>
       <c r="I57" s="3">
-        <v>27600</v>
+        <v>626800</v>
       </c>
       <c r="J57" s="3">
-        <v>23800</v>
+        <v>791200</v>
       </c>
       <c r="K57" s="3">
         <v>14100</v>
@@ -2706,25 +2710,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>190600</v>
+        <v>201000</v>
       </c>
       <c r="E58" s="3">
-        <v>42600</v>
+        <v>593300</v>
       </c>
       <c r="F58" s="3">
-        <v>138500</v>
+        <v>1063300</v>
       </c>
       <c r="G58" s="3">
-        <v>26400</v>
+        <v>264900</v>
       </c>
       <c r="H58" s="3">
-        <v>130000</v>
+        <v>1773900</v>
       </c>
       <c r="I58" s="3">
-        <v>115000</v>
+        <v>1536800</v>
       </c>
       <c r="J58" s="3">
-        <v>41400</v>
+        <v>1373600</v>
       </c>
       <c r="K58" s="3">
         <v>22100</v>
@@ -2751,25 +2755,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>19700</v>
+        <v>11400</v>
       </c>
       <c r="E59" s="3">
-        <v>4900</v>
+        <v>27500</v>
       </c>
       <c r="F59" s="3">
-        <v>36200</v>
+        <v>264000</v>
       </c>
       <c r="G59" s="3">
-        <v>2700</v>
+        <v>19500</v>
       </c>
       <c r="H59" s="3">
-        <v>47600</v>
+        <v>562700</v>
       </c>
       <c r="I59" s="3">
-        <v>14700</v>
+        <v>263000</v>
       </c>
       <c r="J59" s="3">
-        <v>10600</v>
+        <v>268400</v>
       </c>
       <c r="K59" s="3">
         <v>15300</v>
@@ -2796,25 +2800,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>285900</v>
+        <v>301400</v>
       </c>
       <c r="E60" s="3">
-        <v>78800</v>
+        <v>1096100</v>
       </c>
       <c r="F60" s="3">
-        <v>193800</v>
+        <v>1488000</v>
       </c>
       <c r="G60" s="3">
-        <v>37800</v>
+        <v>379300</v>
       </c>
       <c r="H60" s="3">
-        <v>224000</v>
+        <v>3056700</v>
       </c>
       <c r="I60" s="3">
-        <v>109900</v>
+        <v>2497700</v>
       </c>
       <c r="J60" s="3">
-        <v>75800</v>
+        <v>2516700</v>
       </c>
       <c r="K60" s="3">
         <v>51500</v>
@@ -2841,25 +2845,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>202200</v>
+        <v>213200</v>
       </c>
       <c r="E61" s="3">
-        <v>72800</v>
+        <v>1012800</v>
       </c>
       <c r="F61" s="3">
-        <v>31800</v>
+        <v>244500</v>
       </c>
       <c r="G61" s="3">
-        <v>81100</v>
+        <v>815000</v>
       </c>
       <c r="H61" s="3">
-        <v>486100</v>
+        <v>6634200</v>
       </c>
       <c r="I61" s="3">
-        <v>396900</v>
+        <v>9017900</v>
       </c>
       <c r="J61" s="3">
-        <v>292900</v>
+        <v>9719800</v>
       </c>
       <c r="K61" s="3">
         <v>121500</v>
@@ -2886,25 +2890,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>644800</v>
+        <v>65200</v>
       </c>
       <c r="E62" s="3">
-        <v>188800</v>
+        <v>229400</v>
       </c>
       <c r="F62" s="3">
-        <v>229700</v>
+        <v>66200</v>
       </c>
       <c r="G62" s="3">
-        <v>120000</v>
+        <v>27300</v>
       </c>
       <c r="H62" s="3">
-        <v>78100</v>
+        <v>116900</v>
       </c>
       <c r="I62" s="3">
-        <v>71100</v>
+        <v>368200</v>
       </c>
       <c r="J62" s="3">
-        <v>54900</v>
+        <v>389500</v>
       </c>
       <c r="K62" s="3">
         <v>31100</v>
@@ -3066,25 +3070,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1209600</v>
+        <v>1194400</v>
       </c>
       <c r="E66" s="3">
-        <v>363500</v>
+        <v>4736700</v>
       </c>
       <c r="F66" s="3">
-        <v>479700</v>
+        <v>3496100</v>
       </c>
       <c r="G66" s="3">
-        <v>274500</v>
+        <v>2399300</v>
       </c>
       <c r="H66" s="3">
-        <v>890500</v>
+        <v>10756200</v>
       </c>
       <c r="I66" s="3">
-        <v>657800</v>
+        <v>13131000</v>
       </c>
       <c r="J66" s="3">
-        <v>484100</v>
+        <v>14056900</v>
       </c>
       <c r="K66" s="3">
         <v>228000</v>
@@ -3310,25 +3314,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>318900</v>
+        <v>351100</v>
       </c>
       <c r="E72" s="3">
-        <v>149500</v>
+        <v>1949600</v>
       </c>
       <c r="F72" s="3">
-        <v>129100</v>
+        <v>1143800</v>
       </c>
       <c r="G72" s="3">
-        <v>27800</v>
+        <v>364500</v>
       </c>
       <c r="H72" s="3">
-        <v>44300</v>
+        <v>737000</v>
       </c>
       <c r="I72" s="3">
-        <v>17800</v>
+        <v>524500</v>
       </c>
       <c r="J72" s="3">
-        <v>42900</v>
+        <v>1489900</v>
       </c>
       <c r="K72" s="3">
         <v>27000</v>
@@ -3490,25 +3494,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1121800</v>
+        <v>1182700</v>
       </c>
       <c r="E76" s="3">
-        <v>376500</v>
+        <v>5240800</v>
       </c>
       <c r="F76" s="3">
-        <v>356200</v>
+        <v>2734900</v>
       </c>
       <c r="G76" s="3">
-        <v>105400</v>
+        <v>1059200</v>
       </c>
       <c r="H76" s="3">
-        <v>89200</v>
+        <v>1217900</v>
       </c>
       <c r="I76" s="3">
-        <v>47700</v>
+        <v>1083200</v>
       </c>
       <c r="J76" s="3">
-        <v>63800</v>
+        <v>2116600</v>
       </c>
       <c r="K76" s="3">
         <v>28700</v>
@@ -3630,25 +3634,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-19100</v>
+        <v>-20200</v>
       </c>
       <c r="E81" s="3">
-        <v>59600</v>
+        <v>830200</v>
       </c>
       <c r="F81" s="3">
-        <v>77500</v>
+        <v>2210100</v>
       </c>
       <c r="G81" s="3">
-        <v>-110000</v>
+        <v>-1105300</v>
       </c>
       <c r="H81" s="3">
-        <v>36500</v>
+        <v>498200</v>
       </c>
       <c r="I81" s="3">
-        <v>-57200</v>
+        <v>-1299300</v>
       </c>
       <c r="J81" s="3">
-        <v>15300</v>
+        <v>726300</v>
       </c>
       <c r="K81" s="3">
         <v>-1200</v>
@@ -3694,25 +3698,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>6800</v>
+        <v>6000</v>
       </c>
       <c r="E83" s="3">
-        <v>2000</v>
+        <v>21600</v>
       </c>
       <c r="F83" s="3">
-        <v>2100</v>
+        <v>59500</v>
       </c>
       <c r="G83" s="3">
-        <v>2400</v>
+        <v>23700</v>
       </c>
       <c r="H83" s="3">
-        <v>1200</v>
+        <v>16700</v>
       </c>
       <c r="I83" s="3">
-        <v>600</v>
+        <v>13200</v>
       </c>
       <c r="J83" s="3">
-        <v>7000</v>
+        <v>193700</v>
       </c>
       <c r="K83" s="3">
         <v>3700</v>
@@ -3964,25 +3968,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>96300</v>
+        <v>113500</v>
       </c>
       <c r="E89" s="3">
-        <v>36700</v>
+        <v>528300</v>
       </c>
       <c r="F89" s="3">
-        <v>27500</v>
+        <v>810900</v>
       </c>
       <c r="G89" s="3">
-        <v>-529800</v>
+        <v>53800</v>
       </c>
       <c r="H89" s="3">
-        <v>79700</v>
+        <v>1087600</v>
       </c>
       <c r="I89" s="3">
-        <v>42200</v>
+        <v>959700</v>
       </c>
       <c r="J89" s="3">
-        <v>14900</v>
+        <v>704600</v>
       </c>
       <c r="K89" s="3">
         <v>10100</v>
@@ -4027,26 +4031,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-16900</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-14500</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-10100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-9700</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>-4500</v>
@@ -4163,25 +4167,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>86600</v>
+        <v>91300</v>
       </c>
       <c r="E94" s="3">
-        <v>27500</v>
+        <v>382800</v>
       </c>
       <c r="F94" s="3">
-        <v>25100</v>
+        <v>716100</v>
       </c>
       <c r="G94" s="3">
-        <v>247600</v>
+        <v>2487600</v>
       </c>
       <c r="H94" s="3">
-        <v>116800</v>
+        <v>1594000</v>
       </c>
       <c r="I94" s="3">
-        <v>17500</v>
+        <v>397100</v>
       </c>
       <c r="J94" s="3">
-        <v>-22200</v>
+        <v>-1053700</v>
       </c>
       <c r="K94" s="3">
         <v>-2300</v>
@@ -4227,16 +4231,16 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-158500</v>
+        <v>167100</v>
       </c>
       <c r="E96" s="3">
-        <v>-33600</v>
+        <v>467300</v>
       </c>
       <c r="F96" s="3">
-        <v>-400</v>
+        <v>11600</v>
       </c>
       <c r="G96" s="3">
-        <v>-9500</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -4245,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-2700</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4407,25 +4411,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-198600</v>
+        <v>-209400</v>
       </c>
       <c r="E100" s="3">
-        <v>-84400</v>
+        <v>-1174300</v>
       </c>
       <c r="F100" s="3">
-        <v>-30600</v>
+        <v>-874000</v>
       </c>
       <c r="G100" s="3">
-        <v>-177600</v>
+        <v>-1784400</v>
       </c>
       <c r="H100" s="3">
-        <v>-207700</v>
+        <v>-2834400</v>
       </c>
       <c r="I100" s="3">
-        <v>-43400</v>
+        <v>-985000</v>
       </c>
       <c r="J100" s="3">
-        <v>-4500</v>
+        <v>-212700</v>
       </c>
       <c r="K100" s="3">
         <v>1700</v>
@@ -4452,25 +4456,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>11300</v>
+        <v>12000</v>
       </c>
       <c r="E101" s="3">
-        <v>600</v>
+        <v>8300</v>
       </c>
       <c r="F101" s="3">
-        <v>-500</v>
+        <v>-12800</v>
       </c>
       <c r="G101" s="3">
-        <v>-32100</v>
+        <v>-322300</v>
       </c>
       <c r="H101" s="3">
-        <v>22400</v>
+        <v>312500</v>
       </c>
       <c r="I101" s="3">
-        <v>-10600</v>
+        <v>-240200</v>
       </c>
       <c r="J101" s="3">
-        <v>20800</v>
+        <v>985600</v>
       </c>
       <c r="K101" s="3">
         <v>2900</v>
@@ -4497,25 +4501,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-4300</v>
+        <v>7400</v>
       </c>
       <c r="E102" s="3">
-        <v>-19600</v>
+        <v>-255000</v>
       </c>
       <c r="F102" s="3">
-        <v>21500</v>
+        <v>640100</v>
       </c>
       <c r="G102" s="3">
-        <v>-491900</v>
+        <v>434600</v>
       </c>
       <c r="H102" s="3">
-        <v>11200</v>
+        <v>159700</v>
       </c>
       <c r="I102" s="3">
-        <v>5800</v>
+        <v>131700</v>
       </c>
       <c r="J102" s="3">
-        <v>8900</v>
+        <v>423900</v>
       </c>
       <c r="K102" s="3">
         <v>12400</v>
